--- a/research/traditional_assets/database/data/switzerland/switzerland_healthcare_support_services.xlsx
+++ b/research/traditional_assets/database/data/switzerland/switzerland_healthcare_support_services.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08148062653468752</v>
+        <v>0.08140009481994687</v>
       </c>
       <c r="C2">
-        <v>4867.388834979345</v>
+        <v>4827.294064607252</v>
       </c>
       <c r="D2">
-        <v>4789.988834979345</v>
+        <v>4800.241064607252</v>
       </c>
       <c r="E2">
-        <v>-946.1</v>
+        <v>-895.753</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>50.347</v>
       </c>
       <c r="G2">
         <v>77.40000000000001</v>
@@ -1457,28 +1457,28 @@
         <v>151.8</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>2.5324541</v>
       </c>
       <c r="N2">
-        <v>151.8</v>
+        <v>149.2675459</v>
       </c>
       <c r="O2">
-        <v>22.1628</v>
+        <v>21.7930617014</v>
       </c>
       <c r="P2">
-        <v>129.6372</v>
+        <v>127.4744841986</v>
       </c>
       <c r="Q2">
-        <v>246.3372</v>
+        <v>244.1744841986</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08148062653468752</v>
+        <v>0.08178841698984532</v>
       </c>
       <c r="T2">
-        <v>0.8240329453738456</v>
+        <v>0.831141269973333</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>59.9418563992927</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08140009481994687</v>
+        <v>0.08131956310520623</v>
       </c>
       <c r="C3">
-        <v>4827.294064607252</v>
+        <v>4787.243274990174</v>
       </c>
       <c r="D3">
-        <v>4800.241064607252</v>
+        <v>4810.537274990174</v>
       </c>
       <c r="E3">
-        <v>-895.753</v>
+        <v>-845.4060000000001</v>
       </c>
       <c r="F3">
-        <v>50.347</v>
+        <v>100.694</v>
       </c>
       <c r="G3">
         <v>77.40000000000001</v>
@@ -1539,28 +1539,28 @@
         <v>151.8</v>
       </c>
       <c r="M3">
-        <v>2.5324541</v>
+        <v>5.0649082</v>
       </c>
       <c r="N3">
-        <v>149.2675459</v>
+        <v>146.7350918</v>
       </c>
       <c r="O3">
-        <v>21.7930617014</v>
+        <v>21.4233234028</v>
       </c>
       <c r="P3">
-        <v>127.4744841986</v>
+        <v>125.3117683972</v>
       </c>
       <c r="Q3">
-        <v>244.1744841986</v>
+        <v>242.0117683972</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08178841698984532</v>
+        <v>0.08210248888286349</v>
       </c>
       <c r="T3">
-        <v>0.831141269973333</v>
+        <v>0.8383946624217897</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>59.9418563992927</v>
+        <v>29.97092819964635</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08131956310520623</v>
+        <v>0.08123903139046558</v>
       </c>
       <c r="C4">
-        <v>4787.243274990174</v>
+        <v>4747.236749744181</v>
       </c>
       <c r="D4">
-        <v>4810.537274990174</v>
+        <v>4820.877749744182</v>
       </c>
       <c r="E4">
-        <v>-845.4060000000001</v>
+        <v>-795.059</v>
       </c>
       <c r="F4">
-        <v>100.694</v>
+        <v>151.041</v>
       </c>
       <c r="G4">
         <v>77.40000000000001</v>
@@ -1621,28 +1621,28 @@
         <v>151.8</v>
       </c>
       <c r="M4">
-        <v>5.0649082</v>
+        <v>7.597362299999999</v>
       </c>
       <c r="N4">
-        <v>146.7350918</v>
+        <v>144.2026377</v>
       </c>
       <c r="O4">
-        <v>21.4233234028</v>
+        <v>21.0535851042</v>
       </c>
       <c r="P4">
-        <v>125.3117683972</v>
+        <v>123.1490525958</v>
       </c>
       <c r="Q4">
-        <v>242.0117683972</v>
+        <v>239.8490525958</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08210248888286349</v>
+        <v>0.08242303648501606</v>
       </c>
       <c r="T4">
-        <v>0.8383946624217897</v>
+        <v>0.8457976093537197</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>29.97092819964635</v>
+        <v>19.98061879976423</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08123903139046558</v>
+        <v>0.08115849967572494</v>
       </c>
       <c r="C5">
-        <v>4747.236749744181</v>
+        <v>4707.274774929176</v>
       </c>
       <c r="D5">
-        <v>4820.877749744182</v>
+        <v>4831.262774929176</v>
       </c>
       <c r="E5">
-        <v>-795.059</v>
+        <v>-744.712</v>
       </c>
       <c r="F5">
-        <v>151.041</v>
+        <v>201.388</v>
       </c>
       <c r="G5">
         <v>77.40000000000001</v>
@@ -1703,28 +1703,28 @@
         <v>151.8</v>
       </c>
       <c r="M5">
-        <v>7.597362299999999</v>
+        <v>10.1298164</v>
       </c>
       <c r="N5">
-        <v>144.2026377</v>
+        <v>141.6701836</v>
       </c>
       <c r="O5">
-        <v>21.0535851042</v>
+        <v>20.6838468056</v>
       </c>
       <c r="P5">
-        <v>123.1490525958</v>
+        <v>120.9863367944</v>
       </c>
       <c r="Q5">
-        <v>239.8490525958</v>
+        <v>237.6863367944</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08242303648501606</v>
+        <v>0.08275026216221348</v>
       </c>
       <c r="T5">
-        <v>0.8457976093537197</v>
+        <v>0.8533547843467316</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>19.98061879976423</v>
+        <v>14.98546409982317</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08115849967572494</v>
+        <v>0.08114201796098429</v>
       </c>
       <c r="C6">
-        <v>4707.274774929176</v>
+        <v>4659.058704294983</v>
       </c>
       <c r="D6">
-        <v>4831.262774929176</v>
+        <v>4833.393704294983</v>
       </c>
       <c r="E6">
-        <v>-744.712</v>
+        <v>-694.365</v>
       </c>
       <c r="F6">
-        <v>201.388</v>
+        <v>251.735</v>
       </c>
       <c r="G6">
         <v>77.40000000000001</v>
@@ -1785,45 +1785,45 @@
         <v>151.8</v>
       </c>
       <c r="M6">
-        <v>10.1298164</v>
+        <v>13.039873</v>
       </c>
       <c r="N6">
-        <v>141.6701836</v>
+        <v>138.760127</v>
       </c>
       <c r="O6">
-        <v>20.6838468056</v>
+        <v>20.258978542</v>
       </c>
       <c r="P6">
-        <v>120.9863367944</v>
+        <v>118.501148458</v>
       </c>
       <c r="Q6">
-        <v>237.6863367944</v>
+        <v>235.201148458</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08275026216221348</v>
+        <v>0.0830843768010361</v>
       </c>
       <c r="T6">
-        <v>0.8533547843467316</v>
+        <v>0.861071057760649</v>
       </c>
       <c r="U6">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V6">
         <v>0.146</v>
       </c>
       <c r="W6">
-        <v>0.0429562</v>
+        <v>0.0442372</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y6">
-        <v>14.98546409982317</v>
+        <v>11.64121767136843</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08114201796098429</v>
+        <v>0.08116140424624364</v>
       </c>
       <c r="C7">
-        <v>4659.058704294983</v>
+        <v>4606.205436240671</v>
       </c>
       <c r="D7">
-        <v>4833.393704294983</v>
+        <v>4830.887436240671</v>
       </c>
       <c r="E7">
-        <v>-694.365</v>
+        <v>-644.018</v>
       </c>
       <c r="F7">
-        <v>251.735</v>
+        <v>302.082</v>
       </c>
       <c r="G7">
         <v>77.40000000000001</v>
@@ -1867,45 +1867,45 @@
         <v>151.8</v>
       </c>
       <c r="M7">
-        <v>13.039873</v>
+        <v>16.161387</v>
       </c>
       <c r="N7">
-        <v>138.760127</v>
+        <v>135.638613</v>
       </c>
       <c r="O7">
-        <v>20.258978542</v>
+        <v>19.803237498</v>
       </c>
       <c r="P7">
-        <v>118.501148458</v>
+        <v>115.835375502</v>
       </c>
       <c r="Q7">
-        <v>235.201148458</v>
+        <v>232.535375502</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.0830843768010361</v>
+        <v>0.08342560026196133</v>
       </c>
       <c r="T7">
-        <v>0.861071057760649</v>
+        <v>0.8689515072046498</v>
       </c>
       <c r="U7">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V7">
         <v>0.146</v>
       </c>
       <c r="W7">
-        <v>0.0442372</v>
+        <v>0.045689</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y7">
-        <v>11.64121767136843</v>
+        <v>9.39275818344057</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08116140424624364</v>
+        <v>0.08110820053150301</v>
       </c>
       <c r="C8">
-        <v>4606.205436240671</v>
+        <v>4562.742867827464</v>
       </c>
       <c r="D8">
-        <v>4830.887436240671</v>
+        <v>4837.771867827464</v>
       </c>
       <c r="E8">
-        <v>-644.018</v>
+        <v>-593.671</v>
       </c>
       <c r="F8">
-        <v>302.082</v>
+        <v>352.429</v>
       </c>
       <c r="G8">
         <v>77.40000000000001</v>
@@ -1949,28 +1949,28 @@
         <v>151.8</v>
       </c>
       <c r="M8">
-        <v>16.161387</v>
+        <v>18.8549515</v>
       </c>
       <c r="N8">
-        <v>135.638613</v>
+        <v>132.9450485</v>
       </c>
       <c r="O8">
-        <v>19.803237498</v>
+        <v>19.409977081</v>
       </c>
       <c r="P8">
-        <v>115.835375502</v>
+        <v>113.535071419</v>
       </c>
       <c r="Q8">
-        <v>232.535375502</v>
+        <v>230.235071419</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08342560026196133</v>
+        <v>0.0837741618618312</v>
       </c>
       <c r="T8">
-        <v>0.8689515072046498</v>
+        <v>0.8770014286797043</v>
       </c>
       <c r="U8">
         <v>0.0535</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>9.39275818344057</v>
+        <v>8.050935585806201</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08110820053150301</v>
+        <v>0.08110965281676236</v>
       </c>
       <c r="C9">
-        <v>4562.742867827464</v>
+        <v>4512.207685153918</v>
       </c>
       <c r="D9">
-        <v>4837.771867827464</v>
+        <v>4837.583685153918</v>
       </c>
       <c r="E9">
-        <v>-593.671</v>
+        <v>-543.3240000000001</v>
       </c>
       <c r="F9">
-        <v>352.429</v>
+        <v>402.776</v>
       </c>
       <c r="G9">
         <v>77.40000000000001</v>
@@ -2031,45 +2031,45 @@
         <v>151.8</v>
       </c>
       <c r="M9">
-        <v>18.8549515</v>
+        <v>21.8707368</v>
       </c>
       <c r="N9">
-        <v>132.9450485</v>
+        <v>129.9292632</v>
       </c>
       <c r="O9">
-        <v>19.409977081</v>
+        <v>18.9696724272</v>
       </c>
       <c r="P9">
-        <v>113.535071419</v>
+        <v>110.9595907728</v>
       </c>
       <c r="Q9">
-        <v>230.235071419</v>
+        <v>227.6595907728</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.0837741618618312</v>
+        <v>0.08413030088778517</v>
       </c>
       <c r="T9">
-        <v>0.8770014286797043</v>
+        <v>0.8852263484476947</v>
       </c>
       <c r="U9">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V9">
         <v>0.146</v>
       </c>
       <c r="W9">
-        <v>0.045689</v>
+        <v>0.0463722</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y9">
-        <v>8.050935585806201</v>
+        <v>6.940781254337989</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08110965281676236</v>
+        <v>0.08106328110202171</v>
       </c>
       <c r="C10">
-        <v>4512.207685153918</v>
+        <v>4467.876628158951</v>
       </c>
       <c r="D10">
-        <v>4837.583685153918</v>
+        <v>4843.599628158951</v>
       </c>
       <c r="E10">
-        <v>-543.3240000000001</v>
+        <v>-492.977</v>
       </c>
       <c r="F10">
-        <v>402.776</v>
+        <v>453.123</v>
       </c>
       <c r="G10">
         <v>77.40000000000001</v>
@@ -2113,28 +2113,28 @@
         <v>151.8</v>
       </c>
       <c r="M10">
-        <v>21.8707368</v>
+        <v>24.6045789</v>
       </c>
       <c r="N10">
-        <v>129.9292632</v>
+        <v>127.1954211</v>
       </c>
       <c r="O10">
-        <v>18.9696724272</v>
+        <v>18.5705314806</v>
       </c>
       <c r="P10">
-        <v>110.9595907728</v>
+        <v>108.6248896194</v>
       </c>
       <c r="Q10">
-        <v>227.6595907728</v>
+        <v>225.3248896194</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08413030088778517</v>
+        <v>0.08449426714507881</v>
       </c>
       <c r="T10">
-        <v>0.8852263484476947</v>
+        <v>0.8936320356831134</v>
       </c>
       <c r="U10">
         <v>0.0543</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>6.940781254337989</v>
+        <v>6.169583337189323</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08106328110202171</v>
+        <v>0.08110230938728108</v>
       </c>
       <c r="C11">
-        <v>4467.876628158951</v>
+        <v>4412.46537441677</v>
       </c>
       <c r="D11">
-        <v>4843.599628158951</v>
+        <v>4838.535374416771</v>
       </c>
       <c r="E11">
-        <v>-492.977</v>
+        <v>-442.6300000000001</v>
       </c>
       <c r="F11">
-        <v>453.123</v>
+        <v>503.4699999999999</v>
       </c>
       <c r="G11">
         <v>77.40000000000001</v>
@@ -2195,45 +2195,45 @@
         <v>151.8</v>
       </c>
       <c r="M11">
-        <v>24.6045789</v>
+        <v>27.841891</v>
       </c>
       <c r="N11">
-        <v>127.1954211</v>
+        <v>123.958109</v>
       </c>
       <c r="O11">
-        <v>18.5705314806</v>
+        <v>18.097883914</v>
       </c>
       <c r="P11">
-        <v>108.6248896194</v>
+        <v>105.860225086</v>
       </c>
       <c r="Q11">
-        <v>225.3248896194</v>
+        <v>222.560225086</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08449426714507881</v>
+        <v>0.08486632154142343</v>
       </c>
       <c r="T11">
-        <v>0.8936320356831134</v>
+        <v>0.9022245159682083</v>
       </c>
       <c r="U11">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V11">
         <v>0.146</v>
       </c>
       <c r="W11">
-        <v>0.0463722</v>
+        <v>0.0472262</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y11">
-        <v>6.169583337189323</v>
+        <v>5.452215871400402</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08110230938728108</v>
+        <v>0.08106447767254042</v>
       </c>
       <c r="C12">
-        <v>4412.46537441677</v>
+        <v>4367.027205381312</v>
       </c>
       <c r="D12">
-        <v>4838.535374416771</v>
+        <v>4843.444205381313</v>
       </c>
       <c r="E12">
-        <v>-442.63</v>
+        <v>-392.283</v>
       </c>
       <c r="F12">
-        <v>503.47</v>
+        <v>553.817</v>
       </c>
       <c r="G12">
         <v>77.40000000000001</v>
@@ -2277,28 +2277,28 @@
         <v>151.8</v>
       </c>
       <c r="M12">
-        <v>27.841891</v>
+        <v>30.6260801</v>
       </c>
       <c r="N12">
-        <v>123.958109</v>
+        <v>121.1739199</v>
       </c>
       <c r="O12">
-        <v>18.097883914</v>
+        <v>17.6913923054</v>
       </c>
       <c r="P12">
-        <v>105.860225086</v>
+        <v>103.4825275946</v>
       </c>
       <c r="Q12">
-        <v>222.560225086</v>
+        <v>220.1825275946</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08486632154142343</v>
+        <v>0.08524673671071958</v>
       </c>
       <c r="T12">
-        <v>0.9022245159682083</v>
+        <v>0.911010085697912</v>
       </c>
       <c r="U12">
         <v>0.0553</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>5.452215871400401</v>
+        <v>4.956559883091274</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08106447767254042</v>
+        <v>0.08102664595779979</v>
       </c>
       <c r="C13">
-        <v>4367.027205381312</v>
+        <v>4321.599006756773</v>
       </c>
       <c r="D13">
-        <v>4843.444205381313</v>
+        <v>4848.363006756773</v>
       </c>
       <c r="E13">
-        <v>-392.283</v>
+        <v>-341.936</v>
       </c>
       <c r="F13">
-        <v>553.817</v>
+        <v>604.164</v>
       </c>
       <c r="G13">
         <v>77.40000000000001</v>
@@ -2359,28 +2359,28 @@
         <v>151.8</v>
       </c>
       <c r="M13">
-        <v>30.6260801</v>
+        <v>33.4102692</v>
       </c>
       <c r="N13">
-        <v>121.1739199</v>
+        <v>118.3897308</v>
       </c>
       <c r="O13">
-        <v>17.6913923054</v>
+        <v>17.2849006968</v>
       </c>
       <c r="P13">
-        <v>103.4825275946</v>
+        <v>101.1048301032</v>
       </c>
       <c r="Q13">
-        <v>220.1825275946</v>
+        <v>217.8048301032</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08524673671071958</v>
+        <v>0.08563579767931795</v>
       </c>
       <c r="T13">
-        <v>0.911010085697912</v>
+        <v>0.919995327466927</v>
       </c>
       <c r="U13">
         <v>0.0553</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>4.956559883091274</v>
+        <v>4.543513226167001</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08102664595779979</v>
+        <v>0.08126636424305915</v>
       </c>
       <c r="C14">
-        <v>4321.599006756773</v>
+        <v>4240.252162774766</v>
       </c>
       <c r="D14">
-        <v>4848.363006756773</v>
+        <v>4817.363162774767</v>
       </c>
       <c r="E14">
-        <v>-341.936</v>
+        <v>-291.5890000000001</v>
       </c>
       <c r="F14">
-        <v>604.164</v>
+        <v>654.511</v>
       </c>
       <c r="G14">
         <v>77.40000000000001</v>
@@ -2441,45 +2441,45 @@
         <v>151.8</v>
       </c>
       <c r="M14">
-        <v>33.4102692</v>
+        <v>37.8307358</v>
       </c>
       <c r="N14">
-        <v>118.3897308</v>
+        <v>113.9692642</v>
       </c>
       <c r="O14">
-        <v>17.2849006968</v>
+        <v>16.6395125732</v>
       </c>
       <c r="P14">
-        <v>101.1048301032</v>
+        <v>97.3297516268</v>
       </c>
       <c r="Q14">
-        <v>217.8048301032</v>
+        <v>214.0297516268</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08563579767931795</v>
+        <v>0.0860338025782289</v>
       </c>
       <c r="T14">
-        <v>0.919995327466927</v>
+        <v>0.9291871265179886</v>
       </c>
       <c r="U14">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V14">
         <v>0.146</v>
       </c>
       <c r="W14">
-        <v>0.0472262</v>
+        <v>0.0493612</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y14">
-        <v>4.543513226167001</v>
+        <v>4.012610296625529</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08126636424305915</v>
+        <v>0.0816683425283185</v>
       </c>
       <c r="C15">
-        <v>4240.252162774766</v>
+        <v>4138.802493619543</v>
       </c>
       <c r="D15">
-        <v>4817.363162774767</v>
+        <v>4766.260493619544</v>
       </c>
       <c r="E15">
-        <v>-291.5890000000001</v>
+        <v>-241.242</v>
       </c>
       <c r="F15">
-        <v>654.511</v>
+        <v>704.8580000000001</v>
       </c>
       <c r="G15">
         <v>77.40000000000001</v>
@@ -2523,45 +2523,45 @@
         <v>151.8</v>
       </c>
       <c r="M15">
-        <v>37.8307358</v>
+        <v>43.2077954</v>
       </c>
       <c r="N15">
-        <v>113.9692642</v>
+        <v>108.5922046</v>
       </c>
       <c r="O15">
-        <v>16.6395125732</v>
+        <v>15.8544618716</v>
       </c>
       <c r="P15">
-        <v>97.3297516268</v>
+        <v>92.73774272840001</v>
       </c>
       <c r="Q15">
-        <v>214.0297516268</v>
+        <v>209.4377427284</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.0860338025782289</v>
+        <v>0.08644106340502151</v>
       </c>
       <c r="T15">
-        <v>0.9291871265179886</v>
+        <v>0.9385926883376793</v>
       </c>
       <c r="U15">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V15">
         <v>0.146</v>
       </c>
       <c r="W15">
-        <v>0.0493612</v>
+        <v>0.0523502</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y15">
-        <v>4.012610296625529</v>
+        <v>3.513254925290634</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.0816683425283185</v>
+        <v>0.08204043081357786</v>
       </c>
       <c r="C16">
-        <v>4138.802493619543</v>
+        <v>4042.109549149806</v>
       </c>
       <c r="D16">
-        <v>4766.260493619544</v>
+        <v>4719.914549149807</v>
       </c>
       <c r="E16">
-        <v>-241.242</v>
+        <v>-190.895</v>
       </c>
       <c r="F16">
-        <v>704.8580000000001</v>
+        <v>755.205</v>
       </c>
       <c r="G16">
         <v>77.40000000000001</v>
@@ -2605,45 +2605,45 @@
         <v>151.8</v>
       </c>
       <c r="M16">
-        <v>43.2077954</v>
+        <v>48.4086405</v>
       </c>
       <c r="N16">
-        <v>108.5922046</v>
+        <v>103.3913595</v>
       </c>
       <c r="O16">
-        <v>15.8544618716</v>
+        <v>15.095138487</v>
       </c>
       <c r="P16">
-        <v>92.73774272840001</v>
+        <v>88.29622101300001</v>
       </c>
       <c r="Q16">
-        <v>209.4377427284</v>
+        <v>204.996221013</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08644106340502151</v>
+        <v>0.08685790683950337</v>
       </c>
       <c r="T16">
-        <v>0.9385926883376793</v>
+        <v>0.9482195574943041</v>
       </c>
       <c r="U16">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V16">
         <v>0.146</v>
       </c>
       <c r="W16">
-        <v>0.0523502</v>
+        <v>0.0547414</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y16">
-        <v>3.513254925290634</v>
+        <v>3.135803824112763</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08204043081357786</v>
+        <v>0.08314354309883722</v>
       </c>
       <c r="C17">
-        <v>4042.109549149806</v>
+        <v>3859.511465609205</v>
       </c>
       <c r="D17">
-        <v>4719.914549149807</v>
+        <v>4587.663465609206</v>
       </c>
       <c r="E17">
-        <v>-190.8950000000001</v>
+        <v>-140.548</v>
       </c>
       <c r="F17">
-        <v>755.2049999999999</v>
+        <v>805.552</v>
       </c>
       <c r="G17">
         <v>77.40000000000001</v>
@@ -2687,45 +2687,45 @@
         <v>151.8</v>
       </c>
       <c r="M17">
-        <v>48.4086405</v>
+        <v>57.91918880000001</v>
       </c>
       <c r="N17">
-        <v>103.3913595</v>
+        <v>93.88081120000001</v>
       </c>
       <c r="O17">
-        <v>15.095138487</v>
+        <v>13.7065984352</v>
       </c>
       <c r="P17">
-        <v>88.29622101300002</v>
+        <v>80.17421276480002</v>
       </c>
       <c r="Q17">
-        <v>204.996221013</v>
+        <v>196.8742127648</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08685790683950337</v>
+        <v>0.08728467511766336</v>
       </c>
       <c r="T17">
-        <v>0.9482195574943041</v>
+        <v>0.9580756378213245</v>
       </c>
       <c r="U17">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V17">
         <v>0.146</v>
       </c>
       <c r="W17">
-        <v>0.0547414</v>
+        <v>0.0614026</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y17">
-        <v>3.135803824112764</v>
+        <v>2.620893060574081</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08314354309883722</v>
+        <v>0.08381367738409656</v>
       </c>
       <c r="C18">
-        <v>3859.511465609205</v>
+        <v>3732.380863837844</v>
       </c>
       <c r="D18">
-        <v>4587.663465609206</v>
+        <v>4510.879863837844</v>
       </c>
       <c r="E18">
-        <v>-140.548</v>
+        <v>-90.20100000000002</v>
       </c>
       <c r="F18">
-        <v>805.552</v>
+        <v>855.899</v>
       </c>
       <c r="G18">
         <v>77.40000000000001</v>
@@ -2769,45 +2769,45 @@
         <v>151.8</v>
       </c>
       <c r="M18">
-        <v>57.91918880000001</v>
+        <v>64.8771442</v>
       </c>
       <c r="N18">
-        <v>93.88081120000001</v>
+        <v>86.92285580000001</v>
       </c>
       <c r="O18">
-        <v>13.7065984352</v>
+        <v>12.6907369468</v>
       </c>
       <c r="P18">
-        <v>80.17421276480002</v>
+        <v>74.23211885320001</v>
       </c>
       <c r="Q18">
-        <v>196.8742127648</v>
+        <v>190.9321188532</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08728467511766336</v>
+        <v>0.08772172696879105</v>
       </c>
       <c r="T18">
-        <v>0.9580756378213245</v>
+        <v>0.9681692140598395</v>
       </c>
       <c r="U18">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V18">
         <v>0.146</v>
       </c>
       <c r="W18">
-        <v>0.0614026</v>
+        <v>0.0647332</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y18">
-        <v>2.620893060574081</v>
+        <v>2.339807059509873</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08381367738409656</v>
+        <v>0.08395091566935592</v>
       </c>
       <c r="C19">
-        <v>3732.380863837844</v>
+        <v>3666.625178340681</v>
       </c>
       <c r="D19">
-        <v>4510.879863837844</v>
+        <v>4495.471178340682</v>
       </c>
       <c r="E19">
-        <v>-90.20100000000002</v>
+        <v>-39.85399999999993</v>
       </c>
       <c r="F19">
-        <v>855.899</v>
+        <v>906.2460000000001</v>
       </c>
       <c r="G19">
         <v>77.40000000000001</v>
@@ -2851,28 +2851,28 @@
         <v>151.8</v>
       </c>
       <c r="M19">
-        <v>64.8771442</v>
+        <v>68.69344680000002</v>
       </c>
       <c r="N19">
-        <v>86.92285580000001</v>
+        <v>83.10655319999999</v>
       </c>
       <c r="O19">
-        <v>12.6907369468</v>
+        <v>12.1335567672</v>
       </c>
       <c r="P19">
-        <v>74.23211885320001</v>
+        <v>70.97299643279999</v>
       </c>
       <c r="Q19">
-        <v>190.9321188532</v>
+        <v>187.6729964328</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08772172696879105</v>
+        <v>0.08816943862116577</v>
       </c>
       <c r="T19">
-        <v>0.9681692140598395</v>
+        <v>0.9785089750846597</v>
       </c>
       <c r="U19">
         <v>0.07580000000000001</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>2.339807059509873</v>
+        <v>2.20981777842599</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08395091566935593</v>
+        <v>0.08408815395461527</v>
       </c>
       <c r="C20">
-        <v>3666.62517834068</v>
+        <v>3600.974403339686</v>
       </c>
       <c r="D20">
-        <v>4495.47117834068</v>
+        <v>4480.167403339686</v>
       </c>
       <c r="E20">
-        <v>-39.85400000000004</v>
+        <v>10.49299999999994</v>
       </c>
       <c r="F20">
-        <v>906.246</v>
+        <v>956.593</v>
       </c>
       <c r="G20">
         <v>77.40000000000001</v>
@@ -2933,28 +2933,28 @@
         <v>151.8</v>
       </c>
       <c r="M20">
-        <v>68.6934468</v>
+        <v>72.5097494</v>
       </c>
       <c r="N20">
-        <v>83.10655320000001</v>
+        <v>79.29025060000001</v>
       </c>
       <c r="O20">
-        <v>12.1335567672</v>
+        <v>11.5763765876</v>
       </c>
       <c r="P20">
-        <v>70.9729964328</v>
+        <v>67.71387401240001</v>
       </c>
       <c r="Q20">
-        <v>187.6729964328</v>
+        <v>184.4138740124</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08816943862116577</v>
+        <v>0.08862820488224109</v>
       </c>
       <c r="T20">
-        <v>0.9785089750846597</v>
+        <v>0.9891040388508335</v>
       </c>
       <c r="U20">
         <v>0.07580000000000001</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>2.209817778425991</v>
+        <v>2.093511579561465</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08408815395461527</v>
+        <v>0.08665075223987463</v>
       </c>
       <c r="C21">
-        <v>3600.974403339686</v>
+        <v>3282.859710424094</v>
       </c>
       <c r="D21">
-        <v>4480.167403339686</v>
+        <v>4212.399710424094</v>
       </c>
       <c r="E21">
-        <v>10.49299999999994</v>
+        <v>60.84000000000003</v>
       </c>
       <c r="F21">
-        <v>956.593</v>
+        <v>1006.94</v>
       </c>
       <c r="G21">
         <v>77.40000000000001</v>
@@ -3015,45 +3015,45 @@
         <v>151.8</v>
       </c>
       <c r="M21">
-        <v>72.5097494</v>
+        <v>90.6246</v>
       </c>
       <c r="N21">
-        <v>79.29025060000001</v>
+        <v>61.17540000000001</v>
       </c>
       <c r="O21">
-        <v>11.5763765876</v>
+        <v>8.931608400000002</v>
       </c>
       <c r="P21">
-        <v>67.71387401240001</v>
+        <v>52.24379160000001</v>
       </c>
       <c r="Q21">
-        <v>184.4138740124</v>
+        <v>168.9437916</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08862820488224109</v>
+        <v>0.08909844029984329</v>
       </c>
       <c r="T21">
-        <v>0.9891040388508335</v>
+        <v>0.9999639792111616</v>
       </c>
       <c r="U21">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V21">
         <v>0.146</v>
       </c>
       <c r="W21">
-        <v>0.0647332</v>
+        <v>0.07686</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y21">
-        <v>2.093511579561465</v>
+        <v>1.675041876046901</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08665075223987463</v>
+        <v>0.08690925852513399</v>
       </c>
       <c r="C22">
-        <v>3282.859710424094</v>
+        <v>3207.267817702495</v>
       </c>
       <c r="D22">
-        <v>4212.399710424094</v>
+        <v>4187.154817702496</v>
       </c>
       <c r="E22">
-        <v>60.84000000000003</v>
+        <v>111.187</v>
       </c>
       <c r="F22">
-        <v>1006.94</v>
+        <v>1057.287</v>
       </c>
       <c r="G22">
         <v>77.40000000000001</v>
@@ -3097,28 +3097,28 @@
         <v>151.8</v>
       </c>
       <c r="M22">
-        <v>90.6246</v>
+        <v>95.15582999999999</v>
       </c>
       <c r="N22">
-        <v>61.17540000000001</v>
+        <v>56.64417000000002</v>
       </c>
       <c r="O22">
-        <v>8.931608400000002</v>
+        <v>8.270048820000001</v>
       </c>
       <c r="P22">
-        <v>52.24379160000001</v>
+        <v>48.37412118000002</v>
       </c>
       <c r="Q22">
-        <v>168.9437916</v>
+        <v>165.07412118</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08909844029984329</v>
+        <v>0.08958058041156201</v>
       </c>
       <c r="T22">
-        <v>0.9999639792111616</v>
+        <v>1.011098854770485</v>
       </c>
       <c r="U22">
         <v>0.09</v>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>1.675041876046901</v>
+        <v>1.595277977187525</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08690925852513398</v>
+        <v>0.08716776481039336</v>
       </c>
       <c r="C23">
-        <v>3207.267817702497</v>
+        <v>3131.976707452392</v>
       </c>
       <c r="D23">
-        <v>4187.154817702498</v>
+        <v>4162.210707452392</v>
       </c>
       <c r="E23">
-        <v>111.187</v>
+        <v>161.534</v>
       </c>
       <c r="F23">
-        <v>1057.287</v>
+        <v>1107.634</v>
       </c>
       <c r="G23">
         <v>77.40000000000001</v>
@@ -3179,28 +3179,28 @@
         <v>151.8</v>
       </c>
       <c r="M23">
-        <v>95.15582999999999</v>
+        <v>99.68706</v>
       </c>
       <c r="N23">
-        <v>56.64417000000002</v>
+        <v>52.11294000000001</v>
       </c>
       <c r="O23">
-        <v>8.270048820000001</v>
+        <v>7.608489240000001</v>
       </c>
       <c r="P23">
-        <v>48.37412118000002</v>
+        <v>44.50445076000001</v>
       </c>
       <c r="Q23">
-        <v>165.07412118</v>
+        <v>161.20445076</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08958058041156201</v>
+        <v>0.09007508309024789</v>
       </c>
       <c r="T23">
-        <v>1.011098854770485</v>
+        <v>1.022519239959536</v>
       </c>
       <c r="U23">
         <v>0.09</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>1.595277977187525</v>
+        <v>1.522765341860819</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08716776481039336</v>
+        <v>0.0992386813576995</v>
       </c>
       <c r="C24">
-        <v>3131.976707452392</v>
+        <v>2175.78891758503</v>
       </c>
       <c r="D24">
-        <v>4162.210707452392</v>
+        <v>3256.369917585029</v>
       </c>
       <c r="E24">
-        <v>161.534</v>
+        <v>211.881</v>
       </c>
       <c r="F24">
-        <v>1107.634</v>
+        <v>1157.981</v>
       </c>
       <c r="G24">
         <v>77.40000000000001</v>
@@ -3261,45 +3261,45 @@
         <v>151.8</v>
       </c>
       <c r="M24">
-        <v>99.68706</v>
+        <v>169.9916108</v>
       </c>
       <c r="N24">
-        <v>52.11294000000001</v>
+        <v>-18.19161080000001</v>
       </c>
       <c r="O24">
-        <v>7.608489240000001</v>
+        <v>-2.655975176800001</v>
       </c>
       <c r="P24">
-        <v>44.50445076000001</v>
+        <v>-15.53563562320001</v>
       </c>
       <c r="Q24">
-        <v>161.20445076</v>
+        <v>101.1643643768</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09007508309024789</v>
+        <v>0.09074894988045554</v>
       </c>
       <c r="T24">
-        <v>1.022519239959536</v>
+        <v>1.038081983382345</v>
       </c>
       <c r="U24">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V24">
-        <v>0.146</v>
+        <v>0.1303758455826104</v>
       </c>
       <c r="W24">
-        <v>0.07686</v>
+        <v>0.1276608258684728</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y24">
-        <v>1.522765341860819</v>
+        <v>0.8929852437165093</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.0992386813576995</v>
+        <v>0.1002486813576995</v>
       </c>
       <c r="C25">
-        <v>2175.78891758503</v>
+        <v>2067.204067874805</v>
       </c>
       <c r="D25">
-        <v>3256.369917585029</v>
+        <v>3198.132067874805</v>
       </c>
       <c r="E25">
-        <v>211.881</v>
+        <v>262.228</v>
       </c>
       <c r="F25">
-        <v>1157.981</v>
+        <v>1208.328</v>
       </c>
       <c r="G25">
         <v>77.40000000000001</v>
@@ -3343,37 +3343,37 @@
         <v>151.8</v>
       </c>
       <c r="M25">
-        <v>169.9916108</v>
+        <v>177.3825504</v>
       </c>
       <c r="N25">
-        <v>-18.19161080000001</v>
+        <v>-25.5825504</v>
       </c>
       <c r="O25">
-        <v>-2.655975176800001</v>
+        <v>-3.7350523584</v>
       </c>
       <c r="P25">
-        <v>-15.53563562320001</v>
+        <v>-21.8474980416</v>
       </c>
       <c r="Q25">
-        <v>101.1643643768</v>
+        <v>94.8525019584</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09074894988045554</v>
+        <v>0.09134038343151415</v>
       </c>
       <c r="T25">
-        <v>1.038081983382345</v>
+        <v>1.051740956847902</v>
       </c>
       <c r="U25">
         <v>0.1468</v>
       </c>
       <c r="V25">
-        <v>0.1303758455826104</v>
+        <v>0.1249435186833349</v>
       </c>
       <c r="W25">
-        <v>0.1276608258684728</v>
+        <v>0.1284582914572864</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>0.8929852437165093</v>
+        <v>0.8557775252283214</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1002486813576995</v>
+        <v>0.1012586813576995</v>
       </c>
       <c r="C26">
-        <v>2067.204067874805</v>
+        <v>1960.665702923554</v>
       </c>
       <c r="D26">
-        <v>3198.132067874805</v>
+        <v>3141.940702923554</v>
       </c>
       <c r="E26">
-        <v>262.228</v>
+        <v>312.5749999999999</v>
       </c>
       <c r="F26">
-        <v>1208.328</v>
+        <v>1258.675</v>
       </c>
       <c r="G26">
         <v>77.40000000000001</v>
@@ -3425,37 +3425,37 @@
         <v>151.8</v>
       </c>
       <c r="M26">
-        <v>177.3825504</v>
+        <v>184.77349</v>
       </c>
       <c r="N26">
-        <v>-25.5825504</v>
+        <v>-32.97349</v>
       </c>
       <c r="O26">
-        <v>-3.7350523584</v>
+        <v>-4.81412954</v>
       </c>
       <c r="P26">
-        <v>-21.8474980416</v>
+        <v>-28.15936046</v>
       </c>
       <c r="Q26">
-        <v>94.8525019584</v>
+        <v>88.54063954</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09134038343151415</v>
+        <v>0.09194758854393434</v>
       </c>
       <c r="T26">
-        <v>1.051740956847902</v>
+        <v>1.065764169605874</v>
       </c>
       <c r="U26">
         <v>0.1468</v>
       </c>
       <c r="V26">
-        <v>0.1249435186833349</v>
+        <v>0.1199457779360015</v>
       </c>
       <c r="W26">
-        <v>0.1284582914572864</v>
+        <v>0.129191959798995</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.8557775252283214</v>
+        <v>0.8215464242191886</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1012586813576995</v>
+        <v>0.1165964129156865</v>
       </c>
       <c r="C27">
-        <v>1960.665702923554</v>
+        <v>1248.563805665912</v>
       </c>
       <c r="D27">
-        <v>3141.940702923554</v>
+        <v>2480.185805665912</v>
       </c>
       <c r="E27">
-        <v>312.5749999999999</v>
+        <v>362.9219999999999</v>
       </c>
       <c r="F27">
-        <v>1258.675</v>
+        <v>1309.022</v>
       </c>
       <c r="G27">
         <v>77.40000000000001</v>
@@ -3507,45 +3507,45 @@
         <v>151.8</v>
       </c>
       <c r="M27">
-        <v>184.77349</v>
+        <v>262.8516176</v>
       </c>
       <c r="N27">
-        <v>-32.97349</v>
+        <v>-111.0516176</v>
       </c>
       <c r="O27">
-        <v>-4.81412954</v>
+        <v>-16.2135361696</v>
       </c>
       <c r="P27">
-        <v>-28.15936046</v>
+        <v>-94.8380814304</v>
       </c>
       <c r="Q27">
-        <v>88.54063954</v>
+        <v>21.86191856960001</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09194758854393434</v>
+        <v>0.09296003103505099</v>
       </c>
       <c r="T27">
-        <v>1.065764169605874</v>
+        <v>1.089146213280623</v>
       </c>
       <c r="U27">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V27">
-        <v>0.1199457779360015</v>
+        <v>0.08431677233855456</v>
       </c>
       <c r="W27">
-        <v>0.129191959798995</v>
+        <v>0.1838691921144183</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y27">
-        <v>0.8215464242191886</v>
+        <v>0.5775121393051683</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1165964129156865</v>
+        <v>0.1181464129156865</v>
       </c>
       <c r="C28">
-        <v>1248.563805665912</v>
+        <v>1146.526739147826</v>
       </c>
       <c r="D28">
-        <v>2480.185805665912</v>
+        <v>2428.495739147826</v>
       </c>
       <c r="E28">
-        <v>362.9219999999999</v>
+        <v>413.2690000000001</v>
       </c>
       <c r="F28">
-        <v>1309.022</v>
+        <v>1359.369</v>
       </c>
       <c r="G28">
         <v>77.40000000000001</v>
@@ -3589,37 +3589,37 @@
         <v>151.8</v>
       </c>
       <c r="M28">
-        <v>262.8516176</v>
+        <v>272.9612952000001</v>
       </c>
       <c r="N28">
-        <v>-111.0516176</v>
+        <v>-121.1612952</v>
       </c>
       <c r="O28">
-        <v>-16.2135361696</v>
+        <v>-17.6895490992</v>
       </c>
       <c r="P28">
-        <v>-94.8380814304</v>
+        <v>-103.4717461008</v>
       </c>
       <c r="Q28">
-        <v>21.86191856960001</v>
+        <v>13.22825389919997</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09296003103505099</v>
+        <v>0.09360605885744896</v>
       </c>
       <c r="T28">
-        <v>1.089146213280623</v>
+        <v>1.104066024421454</v>
       </c>
       <c r="U28">
         <v>0.2008</v>
       </c>
       <c r="V28">
-        <v>0.08431677233855456</v>
+        <v>0.08119392891860808</v>
       </c>
       <c r="W28">
-        <v>0.1838691921144183</v>
+        <v>0.1844962590731435</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.5775121393051683</v>
+        <v>0.5561228008123842</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1181464129156865</v>
+        <v>0.1196964129156865</v>
       </c>
       <c r="C29">
-        <v>1146.526739147826</v>
+        <v>1046.600252382876</v>
       </c>
       <c r="D29">
-        <v>2428.495739147826</v>
+        <v>2378.916252382876</v>
       </c>
       <c r="E29">
-        <v>413.2690000000001</v>
+        <v>463.6160000000001</v>
       </c>
       <c r="F29">
-        <v>1359.369</v>
+        <v>1409.716</v>
       </c>
       <c r="G29">
         <v>77.40000000000001</v>
@@ -3671,37 +3671,37 @@
         <v>151.8</v>
       </c>
       <c r="M29">
-        <v>272.9612952000001</v>
+        <v>283.0709728</v>
       </c>
       <c r="N29">
-        <v>-121.1612952</v>
+        <v>-131.2709728</v>
       </c>
       <c r="O29">
-        <v>-17.6895490992</v>
+        <v>-19.1655620288</v>
       </c>
       <c r="P29">
-        <v>-103.4717461008</v>
+        <v>-112.1054107712</v>
       </c>
       <c r="Q29">
-        <v>13.22825389919997</v>
+        <v>4.594589228799961</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09360605885744896</v>
+        <v>0.09427003189713573</v>
       </c>
       <c r="T29">
-        <v>1.104066024421454</v>
+        <v>1.119400274760641</v>
       </c>
       <c r="U29">
         <v>0.2008</v>
       </c>
       <c r="V29">
-        <v>0.08119392891860808</v>
+        <v>0.07829414574294351</v>
       </c>
       <c r="W29">
-        <v>0.1844962590731435</v>
+        <v>0.185078535534817</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.5561228008123842</v>
+        <v>0.5362612722119419</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1196964129156865</v>
+        <v>0.1212464129156865</v>
       </c>
       <c r="C30">
-        <v>1046.600252382876</v>
+        <v>948.6576646393696</v>
       </c>
       <c r="D30">
-        <v>2378.916252382876</v>
+        <v>2331.32066463937</v>
       </c>
       <c r="E30">
-        <v>463.6160000000001</v>
+        <v>513.9630000000001</v>
       </c>
       <c r="F30">
-        <v>1409.716</v>
+        <v>1460.063</v>
       </c>
       <c r="G30">
         <v>77.40000000000001</v>
@@ -3753,37 +3753,37 @@
         <v>151.8</v>
       </c>
       <c r="M30">
-        <v>283.0709728</v>
+        <v>293.1806504</v>
       </c>
       <c r="N30">
-        <v>-131.2709728</v>
+        <v>-141.3806504</v>
       </c>
       <c r="O30">
-        <v>-19.1655620288</v>
+        <v>-20.6415749584</v>
       </c>
       <c r="P30">
-        <v>-112.1054107712</v>
+        <v>-120.7390754416</v>
       </c>
       <c r="Q30">
-        <v>4.594589228799961</v>
+        <v>-4.039075441600033</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09427003189713573</v>
+        <v>0.09495270840272921</v>
       </c>
       <c r="T30">
-        <v>1.119400274760641</v>
+        <v>1.135166475813608</v>
       </c>
       <c r="U30">
         <v>0.2008</v>
       </c>
       <c r="V30">
-        <v>0.07829414574294351</v>
+        <v>0.07559434761387648</v>
       </c>
       <c r="W30">
-        <v>0.185078535534817</v>
+        <v>0.1856206549991336</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.5362612722119419</v>
+        <v>0.5177695042046335</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1212464129156865</v>
+        <v>0.1227964129156865</v>
       </c>
       <c r="C31">
-        <v>948.6576646393703</v>
+        <v>852.5822344635208</v>
       </c>
       <c r="D31">
-        <v>2331.32066463937</v>
+        <v>2285.592234463521</v>
       </c>
       <c r="E31">
-        <v>513.9629999999999</v>
+        <v>564.3099999999998</v>
       </c>
       <c r="F31">
-        <v>1460.063</v>
+        <v>1510.41</v>
       </c>
       <c r="G31">
         <v>77.40000000000001</v>
@@ -3835,37 +3835,37 @@
         <v>151.8</v>
       </c>
       <c r="M31">
-        <v>293.1806504</v>
+        <v>303.290328</v>
       </c>
       <c r="N31">
-        <v>-141.3806504</v>
+        <v>-151.490328</v>
       </c>
       <c r="O31">
-        <v>-20.6415749584</v>
+        <v>-22.117587888</v>
       </c>
       <c r="P31">
-        <v>-120.7390754416</v>
+        <v>-129.372740112</v>
       </c>
       <c r="Q31">
-        <v>-4.039075441599977</v>
+        <v>-12.67274011199997</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09495270840272921</v>
+        <v>0.09565488995133961</v>
       </c>
       <c r="T31">
-        <v>1.135166475813608</v>
+        <v>1.151383139753802</v>
       </c>
       <c r="U31">
         <v>0.2008</v>
       </c>
       <c r="V31">
-        <v>0.07559434761387651</v>
+        <v>0.07307453602674729</v>
       </c>
       <c r="W31">
-        <v>0.1856206549991336</v>
+        <v>0.1861266331658291</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.5177695042046336</v>
+        <v>0.5005105207311458</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1227964129156865</v>
+        <v>0.135312516074746</v>
       </c>
       <c r="C32">
-        <v>852.5822344635208</v>
+        <v>489.7233817282092</v>
       </c>
       <c r="D32">
-        <v>2285.592234463521</v>
+        <v>1973.080381728209</v>
       </c>
       <c r="E32">
-        <v>564.3099999999998</v>
+        <v>614.6569999999998</v>
       </c>
       <c r="F32">
-        <v>1510.41</v>
+        <v>1560.757</v>
       </c>
       <c r="G32">
         <v>77.40000000000001</v>
@@ -3917,45 +3917,45 @@
         <v>151.8</v>
       </c>
       <c r="M32">
-        <v>303.290328</v>
+        <v>368.0265006</v>
       </c>
       <c r="N32">
-        <v>-151.490328</v>
+        <v>-216.2265006</v>
       </c>
       <c r="O32">
-        <v>-22.117587888</v>
+        <v>-31.56906908759999</v>
       </c>
       <c r="P32">
-        <v>-129.372740112</v>
+        <v>-184.6574315124</v>
       </c>
       <c r="Q32">
-        <v>-12.67274011199997</v>
+        <v>-67.95743151239996</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09565488995133961</v>
+        <v>0.09654569003622795</v>
       </c>
       <c r="T32">
-        <v>1.151383139753802</v>
+        <v>1.17195588998217</v>
       </c>
       <c r="U32">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>0.07307453602674729</v>
+        <v>0.06022066335947984</v>
       </c>
       <c r="W32">
-        <v>0.1861266331658291</v>
+        <v>0.2215999675798347</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y32">
-        <v>0.5005105207311458</v>
+        <v>0.4124702969827386</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.135312516074746</v>
+        <v>0.137212516074746</v>
       </c>
       <c r="C33">
-        <v>489.7233817282092</v>
+        <v>399.2550932263409</v>
       </c>
       <c r="D33">
-        <v>1973.080381728209</v>
+        <v>1932.959093226341</v>
       </c>
       <c r="E33">
-        <v>614.6569999999998</v>
+        <v>665.004</v>
       </c>
       <c r="F33">
-        <v>1560.757</v>
+        <v>1611.104</v>
       </c>
       <c r="G33">
         <v>77.40000000000001</v>
@@ -3999,37 +3999,37 @@
         <v>151.8</v>
       </c>
       <c r="M33">
-        <v>368.0265006</v>
+        <v>379.8983232</v>
       </c>
       <c r="N33">
-        <v>-216.2265006</v>
+        <v>-228.0983232</v>
       </c>
       <c r="O33">
-        <v>-31.56906908759999</v>
+        <v>-33.30235518720001</v>
       </c>
       <c r="P33">
-        <v>-184.6574315124</v>
+        <v>-194.7959680128</v>
       </c>
       <c r="Q33">
-        <v>-67.95743151239996</v>
+        <v>-78.09596801280001</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09654569003622795</v>
+        <v>0.09729195018381954</v>
       </c>
       <c r="T33">
-        <v>1.17195588998217</v>
+        <v>1.189190535423084</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>0.06022066335947984</v>
+        <v>0.05833876762949607</v>
       </c>
       <c r="W33">
-        <v>0.2215999675798347</v>
+        <v>0.2220437185929648</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.4124702969827386</v>
+        <v>0.3995806002020279</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.137212516074746</v>
+        <v>0.139112516074746</v>
       </c>
       <c r="C34">
-        <v>399.2550932263409</v>
+        <v>310.3859667109291</v>
       </c>
       <c r="D34">
-        <v>1932.959093226341</v>
+        <v>1894.436966710929</v>
       </c>
       <c r="E34">
-        <v>665.004</v>
+        <v>715.351</v>
       </c>
       <c r="F34">
-        <v>1611.104</v>
+        <v>1661.451</v>
       </c>
       <c r="G34">
         <v>77.40000000000001</v>
@@ -4081,37 +4081,37 @@
         <v>151.8</v>
       </c>
       <c r="M34">
-        <v>379.8983232</v>
+        <v>391.7701458</v>
       </c>
       <c r="N34">
-        <v>-228.0983232</v>
+        <v>-239.9701458</v>
       </c>
       <c r="O34">
-        <v>-33.30235518720001</v>
+        <v>-35.0356412868</v>
       </c>
       <c r="P34">
-        <v>-194.7959680128</v>
+        <v>-204.9345045132</v>
       </c>
       <c r="Q34">
-        <v>-78.09596801280001</v>
+        <v>-88.23450451320001</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09729195018381954</v>
+        <v>0.09806048675372731</v>
       </c>
       <c r="T34">
-        <v>1.189190535423084</v>
+        <v>1.206939647892086</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>0.05833876762949607</v>
+        <v>0.05657092618617802</v>
       </c>
       <c r="W34">
-        <v>0.2220437185929648</v>
+        <v>0.2224605756052992</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.3995806002020279</v>
+        <v>0.3874720971656028</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.139112516074746</v>
+        <v>0.141012516074746</v>
       </c>
       <c r="C35">
-        <v>310.3859667109291</v>
+        <v>223.0222608065878</v>
       </c>
       <c r="D35">
-        <v>1894.436966710929</v>
+        <v>1857.420260806588</v>
       </c>
       <c r="E35">
-        <v>715.351</v>
+        <v>765.698</v>
       </c>
       <c r="F35">
-        <v>1661.451</v>
+        <v>1711.798</v>
       </c>
       <c r="G35">
         <v>77.40000000000001</v>
@@ -4163,37 +4163,37 @@
         <v>151.8</v>
       </c>
       <c r="M35">
-        <v>391.7701458</v>
+        <v>403.6419684</v>
       </c>
       <c r="N35">
-        <v>-239.9701458</v>
+        <v>-251.8419684</v>
       </c>
       <c r="O35">
-        <v>-35.0356412868</v>
+        <v>-36.76892738639999</v>
       </c>
       <c r="P35">
-        <v>-204.9345045132</v>
+        <v>-215.0730410136</v>
       </c>
       <c r="Q35">
-        <v>-88.23450451320001</v>
+        <v>-98.3730410136</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09806048675372731</v>
+        <v>0.09885231231060196</v>
       </c>
       <c r="T35">
-        <v>1.206939647892086</v>
+        <v>1.225226612254087</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.05657092618617802</v>
+        <v>0.05490707541599631</v>
       </c>
       <c r="W35">
-        <v>0.2224605756052992</v>
+        <v>0.2228529116169081</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.3874720971656028</v>
+        <v>0.3760758590136734</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.141012516074746</v>
+        <v>0.142912516074746</v>
       </c>
       <c r="C36">
-        <v>223.0222608065878</v>
+        <v>137.0774204287004</v>
       </c>
       <c r="D36">
-        <v>1857.420260806588</v>
+        <v>1821.822420428701</v>
       </c>
       <c r="E36">
-        <v>765.698</v>
+        <v>816.0450000000002</v>
       </c>
       <c r="F36">
-        <v>1711.798</v>
+        <v>1762.145</v>
       </c>
       <c r="G36">
         <v>77.40000000000001</v>
@@ -4245,37 +4245,37 @@
         <v>151.8</v>
       </c>
       <c r="M36">
-        <v>403.6419684</v>
+        <v>415.5137910000001</v>
       </c>
       <c r="N36">
-        <v>-251.8419684</v>
+        <v>-263.7137910000001</v>
       </c>
       <c r="O36">
-        <v>-36.76892738639999</v>
+        <v>-38.50221348600001</v>
       </c>
       <c r="P36">
-        <v>-215.0730410136</v>
+        <v>-225.2115775140001</v>
       </c>
       <c r="Q36">
-        <v>-98.3730410136</v>
+        <v>-108.5115775140001</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09885231231060196</v>
+        <v>0.09966850173076507</v>
       </c>
       <c r="T36">
-        <v>1.225226612254087</v>
+        <v>1.244076252442611</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.05490707541599631</v>
+        <v>0.05333830183268212</v>
       </c>
       <c r="W36">
-        <v>0.2228529116169081</v>
+        <v>0.2232228284278536</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.3760758590136734</v>
+        <v>0.3653308344704255</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.142912516074746</v>
+        <v>0.144812516074746</v>
       </c>
       <c r="C37">
-        <v>137.0774204287004</v>
+        <v>52.47140109935663</v>
       </c>
       <c r="D37">
-        <v>1821.822420428701</v>
+        <v>1787.563401099357</v>
       </c>
       <c r="E37">
-        <v>816.0450000000002</v>
+        <v>866.3920000000002</v>
       </c>
       <c r="F37">
-        <v>1762.145</v>
+        <v>1812.492</v>
       </c>
       <c r="G37">
         <v>77.40000000000001</v>
@@ -4327,37 +4327,37 @@
         <v>151.8</v>
       </c>
       <c r="M37">
-        <v>415.5137910000001</v>
+        <v>427.3856136000001</v>
       </c>
       <c r="N37">
-        <v>-263.7137910000001</v>
+        <v>-275.5856136</v>
       </c>
       <c r="O37">
-        <v>-38.50221348600001</v>
+        <v>-40.2354995856</v>
       </c>
       <c r="P37">
-        <v>-225.2115775140001</v>
+        <v>-235.3501140144</v>
       </c>
       <c r="Q37">
-        <v>-108.5115775140001</v>
+        <v>-118.6501140144</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09966850173076507</v>
+        <v>0.1005101970703083</v>
       </c>
       <c r="T37">
-        <v>1.244076252442611</v>
+        <v>1.263514943887027</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.05333830183268212</v>
+        <v>0.05185668233732984</v>
       </c>
       <c r="W37">
-        <v>0.2232228284278536</v>
+        <v>0.2235721943048576</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.3653308344704255</v>
+        <v>0.3551827557351359</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.144812516074746</v>
+        <v>0.146712516074746</v>
       </c>
       <c r="C38">
-        <v>52.47140109935685</v>
+        <v>-30.86993190721273</v>
       </c>
       <c r="D38">
-        <v>1787.563401099357</v>
+        <v>1754.569068092787</v>
       </c>
       <c r="E38">
-        <v>866.3919999999999</v>
+        <v>916.7389999999999</v>
       </c>
       <c r="F38">
-        <v>1812.492</v>
+        <v>1862.839</v>
       </c>
       <c r="G38">
         <v>77.40000000000001</v>
@@ -4409,37 +4409,37 @@
         <v>151.8</v>
       </c>
       <c r="M38">
-        <v>427.3856136</v>
+        <v>439.2574362</v>
       </c>
       <c r="N38">
-        <v>-275.5856136</v>
+        <v>-287.4574362</v>
       </c>
       <c r="O38">
-        <v>-40.2354995856</v>
+        <v>-41.9687856852</v>
       </c>
       <c r="P38">
-        <v>-235.3501140144</v>
+        <v>-245.4886505148</v>
       </c>
       <c r="Q38">
-        <v>-118.6501140144</v>
+        <v>-128.7886505148</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1005101970703083</v>
+        <v>0.1013786128968211</v>
       </c>
       <c r="T38">
-        <v>1.263514943887027</v>
+        <v>1.283570736647138</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.05185668233732985</v>
+        <v>0.05045515038226688</v>
       </c>
       <c r="W38">
-        <v>0.2235721943048576</v>
+        <v>0.2239026755398615</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.355182755735136</v>
+        <v>0.3455832217963485</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.146712516074746</v>
+        <v>0.148612516074746</v>
       </c>
       <c r="C39">
-        <v>-30.86993190721273</v>
+        <v>-113.0153390827538</v>
       </c>
       <c r="D39">
-        <v>1754.569068092787</v>
+        <v>1722.770660917246</v>
       </c>
       <c r="E39">
-        <v>916.7389999999999</v>
+        <v>967.0859999999999</v>
       </c>
       <c r="F39">
-        <v>1862.839</v>
+        <v>1913.186</v>
       </c>
       <c r="G39">
         <v>77.40000000000001</v>
@@ -4491,37 +4491,37 @@
         <v>151.8</v>
       </c>
       <c r="M39">
-        <v>439.2574362</v>
+        <v>451.1292588</v>
       </c>
       <c r="N39">
-        <v>-287.4574362</v>
+        <v>-299.3292588</v>
       </c>
       <c r="O39">
-        <v>-41.9687856852</v>
+        <v>-43.7020717848</v>
       </c>
       <c r="P39">
-        <v>-245.4886505148</v>
+        <v>-255.6271870152</v>
       </c>
       <c r="Q39">
-        <v>-128.7886505148</v>
+        <v>-138.9271870152</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1013786128968211</v>
+        <v>0.1022750421370924</v>
       </c>
       <c r="T39">
-        <v>1.283570736647138</v>
+        <v>1.304273490464028</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.05045515038226688</v>
+        <v>0.04912738326694407</v>
       </c>
       <c r="W39">
-        <v>0.2239026755398615</v>
+        <v>0.2242157630256546</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.3455832217963485</v>
+        <v>0.3364889264859183</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.148612516074746</v>
+        <v>0.150512516074746</v>
       </c>
       <c r="C40">
-        <v>-113.0153390827538</v>
+        <v>-194.0286850078519</v>
       </c>
       <c r="D40">
-        <v>1722.770660917246</v>
+        <v>1692.104314992148</v>
       </c>
       <c r="E40">
-        <v>967.0859999999999</v>
+        <v>1017.433</v>
       </c>
       <c r="F40">
-        <v>1913.186</v>
+        <v>1963.533</v>
       </c>
       <c r="G40">
         <v>77.40000000000001</v>
@@ -4573,37 +4573,37 @@
         <v>151.8</v>
       </c>
       <c r="M40">
-        <v>451.1292588</v>
+        <v>463.0010814</v>
       </c>
       <c r="N40">
-        <v>-299.3292588</v>
+        <v>-311.2010814</v>
       </c>
       <c r="O40">
-        <v>-43.7020717848</v>
+        <v>-45.43535788439999</v>
       </c>
       <c r="P40">
-        <v>-255.6271870152</v>
+        <v>-265.7657235156</v>
       </c>
       <c r="Q40">
-        <v>-138.9271870152</v>
+        <v>-149.0657235156</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1022750421370924</v>
+        <v>0.1032008624999955</v>
       </c>
       <c r="T40">
-        <v>1.304273490464028</v>
+        <v>1.325655023094585</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.04912738326694407</v>
+        <v>0.04786770677291987</v>
       </c>
       <c r="W40">
-        <v>0.2242157630256546</v>
+        <v>0.2245127947429455</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.3364889264859183</v>
+        <v>0.3278610052939717</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.150512516074746</v>
+        <v>0.152412516074746</v>
       </c>
       <c r="C41">
-        <v>-194.0286850078519</v>
+        <v>-273.9693664816721</v>
       </c>
       <c r="D41">
-        <v>1692.104314992148</v>
+        <v>1662.510633518328</v>
       </c>
       <c r="E41">
-        <v>1017.433</v>
+        <v>1067.78</v>
       </c>
       <c r="F41">
-        <v>1963.533</v>
+        <v>2013.88</v>
       </c>
       <c r="G41">
         <v>77.40000000000001</v>
@@ -4655,37 +4655,37 @@
         <v>151.8</v>
       </c>
       <c r="M41">
-        <v>463.0010814</v>
+        <v>474.8729040000001</v>
       </c>
       <c r="N41">
-        <v>-311.2010814</v>
+        <v>-323.0729040000001</v>
       </c>
       <c r="O41">
-        <v>-45.43535788439999</v>
+        <v>-47.16864398400001</v>
       </c>
       <c r="P41">
-        <v>-265.7657235156</v>
+        <v>-275.904260016</v>
       </c>
       <c r="Q41">
-        <v>-149.0657235156</v>
+        <v>-159.204260016</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1032008624999955</v>
+        <v>0.1041575435416622</v>
       </c>
       <c r="T41">
-        <v>1.325655023094585</v>
+        <v>1.347749273479495</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.04786770677291987</v>
+        <v>0.04667101410359686</v>
       </c>
       <c r="W41">
-        <v>0.2245127947429455</v>
+        <v>0.2247949748743719</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.3278610052939717</v>
+        <v>0.3196644801616223</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.152412516074746</v>
+        <v>0.154312516074746</v>
       </c>
       <c r="C42">
-        <v>-273.9693664816721</v>
+        <v>-352.8926964978352</v>
       </c>
       <c r="D42">
-        <v>1662.510633518328</v>
+        <v>1633.934303502165</v>
       </c>
       <c r="E42">
-        <v>1067.78</v>
+        <v>1118.127</v>
       </c>
       <c r="F42">
-        <v>2013.88</v>
+        <v>2064.227</v>
       </c>
       <c r="G42">
         <v>77.40000000000001</v>
@@ -4737,37 +4737,37 @@
         <v>151.8</v>
       </c>
       <c r="M42">
-        <v>474.8729040000001</v>
+        <v>486.7447266</v>
       </c>
       <c r="N42">
-        <v>-323.0729040000001</v>
+        <v>-334.9447266</v>
       </c>
       <c r="O42">
-        <v>-47.16864398400001</v>
+        <v>-48.90193008359999</v>
       </c>
       <c r="P42">
-        <v>-275.904260016</v>
+        <v>-286.0427965164</v>
       </c>
       <c r="Q42">
-        <v>-159.204260016</v>
+        <v>-169.3427965164</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1041575435416622</v>
+        <v>0.1051466544491479</v>
       </c>
       <c r="T42">
-        <v>1.347749273479495</v>
+        <v>1.370592481504571</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.04667101410359686</v>
+        <v>0.04553269668643597</v>
       </c>
       <c r="W42">
-        <v>0.2247949748743719</v>
+        <v>0.2250633901213384</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.3196644801616223</v>
+        <v>0.311867785523534</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.154312516074746</v>
+        <v>0.156212516074746</v>
       </c>
       <c r="C43">
-        <v>-352.8926964978352</v>
+        <v>-430.8502492892896</v>
       </c>
       <c r="D43">
-        <v>1633.934303502165</v>
+        <v>1606.32375071071</v>
       </c>
       <c r="E43">
-        <v>1118.127</v>
+        <v>1168.474</v>
       </c>
       <c r="F43">
-        <v>2064.227</v>
+        <v>2114.574</v>
       </c>
       <c r="G43">
         <v>77.40000000000001</v>
@@ -4819,37 +4819,37 @@
         <v>151.8</v>
       </c>
       <c r="M43">
-        <v>486.7447266</v>
+        <v>498.6165492</v>
       </c>
       <c r="N43">
-        <v>-334.9447266</v>
+        <v>-346.8165492</v>
       </c>
       <c r="O43">
-        <v>-48.90193008359999</v>
+        <v>-50.63521618319999</v>
       </c>
       <c r="P43">
-        <v>-286.0427965164</v>
+        <v>-296.1813330168</v>
       </c>
       <c r="Q43">
-        <v>-169.3427965164</v>
+        <v>-179.4813330168</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1051466544491479</v>
+        <v>0.1061698726293057</v>
       </c>
       <c r="T43">
-        <v>1.370592481504571</v>
+        <v>1.394223386358099</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.04553269668643597</v>
+        <v>0.04444858486056844</v>
       </c>
       <c r="W43">
-        <v>0.2250633901213384</v>
+        <v>0.225319023689878</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.311867785523534</v>
+        <v>0.304442362058688</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.156212516074746</v>
+        <v>0.158112516074746</v>
       </c>
       <c r="C44">
-        <v>-430.8502492892896</v>
+        <v>-507.8901709706809</v>
       </c>
       <c r="D44">
-        <v>1606.32375071071</v>
+        <v>1579.630829029319</v>
       </c>
       <c r="E44">
-        <v>1168.474</v>
+        <v>1218.821</v>
       </c>
       <c r="F44">
-        <v>2114.574</v>
+        <v>2164.921</v>
       </c>
       <c r="G44">
         <v>77.40000000000001</v>
@@ -4901,37 +4901,37 @@
         <v>151.8</v>
       </c>
       <c r="M44">
-        <v>498.6165492</v>
+        <v>510.4883718</v>
       </c>
       <c r="N44">
-        <v>-346.8165492</v>
+        <v>-358.6883718</v>
       </c>
       <c r="O44">
-        <v>-50.63521618319999</v>
+        <v>-52.36850228279999</v>
       </c>
       <c r="P44">
-        <v>-296.1813330168</v>
+        <v>-306.3198695172</v>
       </c>
       <c r="Q44">
-        <v>-179.4813330168</v>
+        <v>-189.6198695172</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1061698726293057</v>
+        <v>0.1072289932017496</v>
       </c>
       <c r="T44">
-        <v>1.394223386358098</v>
+        <v>1.41868344576789</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.04444858486056844</v>
+        <v>0.04341489684055522</v>
       </c>
       <c r="W44">
-        <v>0.225319023689878</v>
+        <v>0.2255627673249971</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.304442362058688</v>
+        <v>0.2973623071270906</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.158112516074746</v>
+        <v>0.160012516074746</v>
       </c>
       <c r="C45">
-        <v>-507.8901709706809</v>
+        <v>-584.057459714596</v>
       </c>
       <c r="D45">
-        <v>1579.630829029319</v>
+        <v>1553.810540285404</v>
       </c>
       <c r="E45">
-        <v>1218.821</v>
+        <v>1269.168</v>
       </c>
       <c r="F45">
-        <v>2164.921</v>
+        <v>2215.268</v>
       </c>
       <c r="G45">
         <v>77.40000000000001</v>
@@ -4983,37 +4983,37 @@
         <v>151.8</v>
       </c>
       <c r="M45">
-        <v>510.4883718</v>
+        <v>522.3601944000001</v>
       </c>
       <c r="N45">
-        <v>-358.6883718</v>
+        <v>-370.5601944000001</v>
       </c>
       <c r="O45">
-        <v>-52.36850228279999</v>
+        <v>-54.1017883824</v>
       </c>
       <c r="P45">
-        <v>-306.3198695172</v>
+        <v>-316.4584060176001</v>
       </c>
       <c r="Q45">
-        <v>-189.6198695172</v>
+        <v>-199.7584060176001</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1072289932017496</v>
+        <v>0.1083259395089237</v>
       </c>
       <c r="T45">
-        <v>1.41868344576789</v>
+        <v>1.444017078728031</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.04341489684055522</v>
+        <v>0.04242819463963351</v>
       </c>
       <c r="W45">
-        <v>0.2255627673249971</v>
+        <v>0.2257954317039744</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.2973623071270906</v>
+        <v>0.2906040728742021</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.160012516074746</v>
+        <v>0.161912516074746</v>
       </c>
       <c r="C46">
-        <v>-584.057459714596</v>
+        <v>-659.3942188915389</v>
       </c>
       <c r="D46">
-        <v>1553.810540285404</v>
+        <v>1528.820781108461</v>
       </c>
       <c r="E46">
-        <v>1269.168</v>
+        <v>1319.515</v>
       </c>
       <c r="F46">
-        <v>2215.268</v>
+        <v>2265.615</v>
       </c>
       <c r="G46">
         <v>77.40000000000001</v>
@@ -5065,37 +5065,37 @@
         <v>151.8</v>
       </c>
       <c r="M46">
-        <v>522.3601944000001</v>
+        <v>534.2320169999999</v>
       </c>
       <c r="N46">
-        <v>-370.5601944000001</v>
+        <v>-382.4320169999999</v>
       </c>
       <c r="O46">
-        <v>-54.1017883824</v>
+        <v>-55.83507448199998</v>
       </c>
       <c r="P46">
-        <v>-316.4584060176001</v>
+        <v>-326.5969425179999</v>
       </c>
       <c r="Q46">
-        <v>-199.7584060176001</v>
+        <v>-209.8969425179999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1083259395089237</v>
+        <v>0.1094627747727223</v>
       </c>
       <c r="T46">
-        <v>1.444017078728031</v>
+        <v>1.470271934704904</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.04242819463963351</v>
+        <v>0.04148534586986389</v>
       </c>
       <c r="W46">
-        <v>0.2257954317039744</v>
+        <v>0.2260177554438861</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.2906040728742021</v>
+        <v>0.2841462045881088</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.161912516074746</v>
+        <v>0.163812516074746</v>
       </c>
       <c r="C47">
-        <v>-659.3942188915389</v>
+        <v>-733.9398861692291</v>
       </c>
       <c r="D47">
-        <v>1528.820781108461</v>
+        <v>1504.622113830771</v>
       </c>
       <c r="E47">
-        <v>1319.515</v>
+        <v>1369.862</v>
       </c>
       <c r="F47">
-        <v>2265.615</v>
+        <v>2315.962</v>
       </c>
       <c r="G47">
         <v>77.40000000000001</v>
@@ -5147,37 +5147,37 @@
         <v>151.8</v>
       </c>
       <c r="M47">
-        <v>534.2320169999999</v>
+        <v>546.1038396</v>
       </c>
       <c r="N47">
-        <v>-382.4320169999999</v>
+        <v>-394.3038396</v>
       </c>
       <c r="O47">
-        <v>-55.83507448199998</v>
+        <v>-57.5683605816</v>
       </c>
       <c r="P47">
-        <v>-326.5969425179999</v>
+        <v>-336.7354790184</v>
       </c>
       <c r="Q47">
-        <v>-209.8969425179999</v>
+        <v>-220.0354790184</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1094627747727223</v>
+        <v>0.1106417150462913</v>
       </c>
       <c r="T47">
-        <v>1.470271934704904</v>
+        <v>1.497499192754995</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.04148534586986389</v>
+        <v>0.04058349052486684</v>
       </c>
       <c r="W47">
-        <v>0.2260177554438861</v>
+        <v>0.2262304129342364</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.2841462045881088</v>
+        <v>0.2779691131840195</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.163812516074746</v>
+        <v>0.165712516074746</v>
       </c>
       <c r="C48">
-        <v>-733.9398861692291</v>
+        <v>-807.7314411933669</v>
       </c>
       <c r="D48">
-        <v>1504.622113830771</v>
+        <v>1481.177558806633</v>
       </c>
       <c r="E48">
-        <v>1369.862</v>
+        <v>1420.209</v>
       </c>
       <c r="F48">
-        <v>2315.962</v>
+        <v>2366.309</v>
       </c>
       <c r="G48">
         <v>77.40000000000001</v>
@@ -5229,37 +5229,37 @@
         <v>151.8</v>
       </c>
       <c r="M48">
-        <v>546.1038396</v>
+        <v>557.9756622000001</v>
       </c>
       <c r="N48">
-        <v>-394.3038396</v>
+        <v>-406.1756622000001</v>
       </c>
       <c r="O48">
-        <v>-57.5683605816</v>
+        <v>-59.30164668120001</v>
       </c>
       <c r="P48">
-        <v>-336.7354790184</v>
+        <v>-346.8740155188001</v>
       </c>
       <c r="Q48">
-        <v>-220.0354790184</v>
+        <v>-230.1740155188001</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1106417150462913</v>
+        <v>0.1118651436320703</v>
       </c>
       <c r="T48">
-        <v>1.497499192754995</v>
+        <v>1.525753894505089</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.04058349052486684</v>
+        <v>0.03972001200306115</v>
       </c>
       <c r="W48">
-        <v>0.2262304129342364</v>
+        <v>0.2264340211696782</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.2779691131840195</v>
+        <v>0.2720548767332956</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.165712516074746</v>
+        <v>0.1676125160747461</v>
       </c>
       <c r="C49">
-        <v>-807.7314411933669</v>
+        <v>-880.8035941501962</v>
       </c>
       <c r="D49">
-        <v>1481.177558806633</v>
+        <v>1458.452405849804</v>
       </c>
       <c r="E49">
-        <v>1420.209</v>
+        <v>1470.556</v>
       </c>
       <c r="F49">
-        <v>2366.309</v>
+        <v>2416.656</v>
       </c>
       <c r="G49">
         <v>77.40000000000001</v>
@@ -5311,37 +5311,37 @@
         <v>151.8</v>
       </c>
       <c r="M49">
-        <v>557.9756622000001</v>
+        <v>569.8474848</v>
       </c>
       <c r="N49">
-        <v>-406.1756622000001</v>
+        <v>-418.0474847999999</v>
       </c>
       <c r="O49">
-        <v>-59.30164668120001</v>
+        <v>-61.03493278079999</v>
       </c>
       <c r="P49">
-        <v>-346.8740155188001</v>
+        <v>-357.0125520192</v>
       </c>
       <c r="Q49">
-        <v>-230.1740155188001</v>
+        <v>-240.3125520192</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1118651436320703</v>
+        <v>0.1131356271634563</v>
       </c>
       <c r="T49">
-        <v>1.525753894505089</v>
+        <v>1.555095315553264</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.03972001200306115</v>
+        <v>0.03889251175299739</v>
       </c>
       <c r="W49">
-        <v>0.2264340211696782</v>
+        <v>0.2266291457286432</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.2720548767332956</v>
+        <v>0.266387066801352</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.167612516074746</v>
+        <v>0.169512516074746</v>
       </c>
       <c r="C50">
-        <v>-880.8035941501962</v>
+        <v>-953.1889572330902</v>
       </c>
       <c r="D50">
-        <v>1458.452405849804</v>
+        <v>1436.414042766909</v>
       </c>
       <c r="E50">
-        <v>1470.556</v>
+        <v>1520.903</v>
       </c>
       <c r="F50">
-        <v>2416.656</v>
+        <v>2467.003</v>
       </c>
       <c r="G50">
         <v>77.40000000000001</v>
@@ -5393,37 +5393,37 @@
         <v>151.8</v>
       </c>
       <c r="M50">
-        <v>569.8474848</v>
+        <v>581.7193073999999</v>
       </c>
       <c r="N50">
-        <v>-418.0474847999999</v>
+        <v>-429.9193073999999</v>
       </c>
       <c r="O50">
-        <v>-61.03493278079999</v>
+        <v>-62.76821888039998</v>
       </c>
       <c r="P50">
-        <v>-357.0125520192</v>
+        <v>-367.1510885196</v>
       </c>
       <c r="Q50">
-        <v>-240.3125520192</v>
+        <v>-250.4510885196</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1131356271634563</v>
+        <v>0.114455933578426</v>
       </c>
       <c r="T50">
-        <v>1.555095315553264</v>
+        <v>1.585587380564112</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.03889251175299739</v>
+        <v>0.03809878702334438</v>
       </c>
       <c r="W50">
-        <v>0.2266291457286432</v>
+        <v>0.2268163060198954</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.266387066801352</v>
+        <v>0.260950596050304</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.169512516074746</v>
+        <v>0.171412516074746</v>
       </c>
       <c r="C51">
-        <v>-953.1889572330902</v>
+        <v>-1024.918200794586</v>
       </c>
       <c r="D51">
-        <v>1436.414042766909</v>
+        <v>1415.031799205414</v>
       </c>
       <c r="E51">
-        <v>1520.903</v>
+        <v>1571.25</v>
       </c>
       <c r="F51">
-        <v>2467.003</v>
+        <v>2517.35</v>
       </c>
       <c r="G51">
         <v>77.40000000000001</v>
@@ -5475,37 +5475,37 @@
         <v>151.8</v>
       </c>
       <c r="M51">
-        <v>581.7193073999999</v>
+        <v>593.59113</v>
       </c>
       <c r="N51">
-        <v>-429.9193073999999</v>
+        <v>-441.79113</v>
       </c>
       <c r="O51">
-        <v>-62.76821888039998</v>
+        <v>-64.50150497999999</v>
       </c>
       <c r="P51">
-        <v>-367.1510885196</v>
+        <v>-377.28962502</v>
       </c>
       <c r="Q51">
-        <v>-250.4510885196</v>
+        <v>-260.58962502</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.114455933578426</v>
+        <v>0.1158290522499946</v>
       </c>
       <c r="T51">
-        <v>1.585587380564112</v>
+        <v>1.617299128175394</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.03809878702334438</v>
+        <v>0.0373368112828775</v>
       </c>
       <c r="W51">
-        <v>0.2268163060198954</v>
+        <v>0.2269959798994975</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.260950596050304</v>
+        <v>0.2557315841292979</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.171412516074746</v>
+        <v>0.173312516074746</v>
       </c>
       <c r="C52">
-        <v>-1024.918200794586</v>
+        <v>-1096.020195756245</v>
       </c>
       <c r="D52">
-        <v>1415.031799205414</v>
+        <v>1394.276804243755</v>
       </c>
       <c r="E52">
-        <v>1571.25</v>
+        <v>1621.597</v>
       </c>
       <c r="F52">
-        <v>2517.35</v>
+        <v>2567.697</v>
       </c>
       <c r="G52">
         <v>77.40000000000001</v>
@@ -5557,37 +5557,37 @@
         <v>151.8</v>
       </c>
       <c r="M52">
-        <v>593.59113</v>
+        <v>605.4629526000001</v>
       </c>
       <c r="N52">
-        <v>-441.79113</v>
+        <v>-453.6629526000001</v>
       </c>
       <c r="O52">
-        <v>-64.50150497999999</v>
+        <v>-66.23479107960001</v>
       </c>
       <c r="P52">
-        <v>-377.28962502</v>
+        <v>-387.4281615204001</v>
       </c>
       <c r="Q52">
-        <v>-260.58962502</v>
+        <v>-270.7281615204001</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1158290522499946</v>
+        <v>0.1172582165816271</v>
       </c>
       <c r="T52">
-        <v>1.617299128175394</v>
+        <v>1.650305232832035</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.0373368112828775</v>
+        <v>0.03660471694399754</v>
       </c>
       <c r="W52">
-        <v>0.2269959798994975</v>
+        <v>0.2271686077446054</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.2557315841292979</v>
+        <v>0.2507172393424489</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.173312516074746</v>
+        <v>0.175212516074746</v>
       </c>
       <c r="C53">
-        <v>-1096.020195756245</v>
+        <v>-1166.522143666896</v>
       </c>
       <c r="D53">
-        <v>1394.276804243755</v>
+        <v>1374.121856333103</v>
       </c>
       <c r="E53">
-        <v>1621.597</v>
+        <v>1671.944</v>
       </c>
       <c r="F53">
-        <v>2567.697</v>
+        <v>2618.044</v>
       </c>
       <c r="G53">
         <v>77.40000000000001</v>
@@ -5639,37 +5639,37 @@
         <v>151.8</v>
       </c>
       <c r="M53">
-        <v>605.4629526000001</v>
+        <v>617.3347752</v>
       </c>
       <c r="N53">
-        <v>-453.6629526000001</v>
+        <v>-465.5347752</v>
       </c>
       <c r="O53">
-        <v>-66.23479107960001</v>
+        <v>-67.96807717919999</v>
       </c>
       <c r="P53">
-        <v>-387.4281615204001</v>
+        <v>-397.5666980207999</v>
       </c>
       <c r="Q53">
-        <v>-270.7281615204001</v>
+        <v>-280.8666980208</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1172582165816271</v>
+        <v>0.1187469294270777</v>
       </c>
       <c r="T53">
-        <v>1.650305232832035</v>
+        <v>1.684686591849369</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.03660471694399754</v>
+        <v>0.0359007800796899</v>
       </c>
       <c r="W53">
-        <v>0.2271686077446054</v>
+        <v>0.2273345960572091</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.2507172393424489</v>
+        <v>0.2458957539704788</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.175212516074746</v>
+        <v>0.177112516074746</v>
       </c>
       <c r="C54">
-        <v>-1166.522143666896</v>
+        <v>-1236.449695641282</v>
       </c>
       <c r="D54">
-        <v>1374.121856333103</v>
+        <v>1354.541304358718</v>
       </c>
       <c r="E54">
-        <v>1671.944</v>
+        <v>1722.291</v>
       </c>
       <c r="F54">
-        <v>2618.044</v>
+        <v>2668.391</v>
       </c>
       <c r="G54">
         <v>77.40000000000001</v>
@@ -5721,37 +5721,37 @@
         <v>151.8</v>
       </c>
       <c r="M54">
-        <v>617.3347752</v>
+        <v>629.2065978000001</v>
       </c>
       <c r="N54">
-        <v>-465.5347752</v>
+        <v>-477.4065978</v>
       </c>
       <c r="O54">
-        <v>-67.96807717919999</v>
+        <v>-69.7013632788</v>
       </c>
       <c r="P54">
-        <v>-397.5666980207999</v>
+        <v>-407.7052345212001</v>
       </c>
       <c r="Q54">
-        <v>-280.8666980208</v>
+        <v>-291.0052345212001</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1187469294270777</v>
+        <v>0.1202989917553134</v>
       </c>
       <c r="T54">
-        <v>1.684686591849369</v>
+        <v>1.720530987420632</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.0359007800796899</v>
+        <v>0.03522340687063914</v>
       </c>
       <c r="W54">
-        <v>0.2273345960572091</v>
+        <v>0.2274943206599033</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.2458957539704788</v>
+        <v>0.2412562114427339</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.177112516074746</v>
+        <v>0.179012516074746</v>
       </c>
       <c r="C55">
-        <v>-1236.449695641282</v>
+        <v>-1305.827061272677</v>
       </c>
       <c r="D55">
-        <v>1354.541304358718</v>
+        <v>1335.510938727323</v>
       </c>
       <c r="E55">
-        <v>1722.291</v>
+        <v>1772.638</v>
       </c>
       <c r="F55">
-        <v>2668.391</v>
+        <v>2718.738</v>
       </c>
       <c r="G55">
         <v>77.40000000000001</v>
@@ -5803,37 +5803,37 @@
         <v>151.8</v>
       </c>
       <c r="M55">
-        <v>629.2065978000001</v>
+        <v>641.0784204000001</v>
       </c>
       <c r="N55">
-        <v>-477.4065978</v>
+        <v>-489.2784204000001</v>
       </c>
       <c r="O55">
-        <v>-69.7013632788</v>
+        <v>-71.43464937840001</v>
       </c>
       <c r="P55">
-        <v>-407.7052345212001</v>
+        <v>-417.8437710216001</v>
       </c>
       <c r="Q55">
-        <v>-291.0052345212001</v>
+        <v>-301.1437710216001</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1202989917553134</v>
+        <v>0.1219185350543419</v>
       </c>
       <c r="T55">
-        <v>1.720530987420632</v>
+        <v>1.757933834973255</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.03522340687063914</v>
+        <v>0.03457112155821989</v>
       </c>
       <c r="W55">
-        <v>0.2274943206599033</v>
+        <v>0.2276481295365718</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.2412562114427339</v>
+        <v>0.236788503823424</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.179012516074746</v>
+        <v>0.1809125160747461</v>
       </c>
       <c r="C56">
-        <v>-1305.827061272677</v>
+        <v>-1374.677108491824</v>
       </c>
       <c r="D56">
-        <v>1335.510938727323</v>
+        <v>1317.007891508176</v>
       </c>
       <c r="E56">
-        <v>1772.638</v>
+        <v>1822.985</v>
       </c>
       <c r="F56">
-        <v>2718.738</v>
+        <v>2769.085</v>
       </c>
       <c r="G56">
         <v>77.40000000000001</v>
@@ -5885,37 +5885,37 @@
         <v>151.8</v>
       </c>
       <c r="M56">
-        <v>641.0784204000001</v>
+        <v>652.950243</v>
       </c>
       <c r="N56">
-        <v>-489.2784204000001</v>
+        <v>-501.150243</v>
       </c>
       <c r="O56">
-        <v>-71.43464937840001</v>
+        <v>-73.16793547799999</v>
       </c>
       <c r="P56">
-        <v>-417.8437710216001</v>
+        <v>-427.982307522</v>
       </c>
       <c r="Q56">
-        <v>-301.1437710216001</v>
+        <v>-311.282307522</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1219185350543419</v>
+        <v>0.1236100580555495</v>
       </c>
       <c r="T56">
-        <v>1.757933834973255</v>
+        <v>1.796999031305994</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.03457112155821989</v>
+        <v>0.03394255571170681</v>
       </c>
       <c r="W56">
-        <v>0.2276481295365718</v>
+        <v>0.2277963453631796</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.236788503823424</v>
+        <v>0.2324832582993618</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1809125160747461</v>
+        <v>0.1828125160747461</v>
       </c>
       <c r="C57">
-        <v>-1374.677108491824</v>
+        <v>-1443.021455238232</v>
       </c>
       <c r="D57">
-        <v>1317.007891508176</v>
+        <v>1299.010544761768</v>
       </c>
       <c r="E57">
-        <v>1822.985</v>
+        <v>1873.332</v>
       </c>
       <c r="F57">
-        <v>2769.085</v>
+        <v>2819.432</v>
       </c>
       <c r="G57">
         <v>77.40000000000001</v>
@@ -5967,37 +5967,37 @@
         <v>151.8</v>
       </c>
       <c r="M57">
-        <v>652.950243</v>
+        <v>664.8220656000001</v>
       </c>
       <c r="N57">
-        <v>-501.150243</v>
+        <v>-513.0220656000001</v>
       </c>
       <c r="O57">
-        <v>-73.16793547799999</v>
+        <v>-74.90122157760001</v>
       </c>
       <c r="P57">
-        <v>-427.982307522</v>
+        <v>-438.1208440224001</v>
       </c>
       <c r="Q57">
-        <v>-311.282307522</v>
+        <v>-321.4208440224001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1236100580555495</v>
+        <v>0.1253784684659029</v>
       </c>
       <c r="T57">
-        <v>1.796999031305994</v>
+        <v>1.83783991838113</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.03394255571170681</v>
+        <v>0.03333643864542633</v>
       </c>
       <c r="W57">
-        <v>0.2277963453631796</v>
+        <v>0.2279392677674085</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.2324832582993618</v>
+        <v>0.2283317715440158</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1828125160747461</v>
+        <v>0.184712516074746</v>
       </c>
       <c r="C58">
-        <v>-1443.021455238232</v>
+        <v>-1510.880553716499</v>
       </c>
       <c r="D58">
-        <v>1299.010544761768</v>
+        <v>1281.4984462835</v>
       </c>
       <c r="E58">
-        <v>1873.332</v>
+        <v>1923.679</v>
       </c>
       <c r="F58">
-        <v>2819.432</v>
+        <v>2869.779</v>
       </c>
       <c r="G58">
         <v>77.40000000000001</v>
@@ -6049,37 +6049,37 @@
         <v>151.8</v>
       </c>
       <c r="M58">
-        <v>664.8220656000001</v>
+        <v>676.6938882000001</v>
       </c>
       <c r="N58">
-        <v>-513.0220656000001</v>
+        <v>-524.8938882</v>
       </c>
       <c r="O58">
-        <v>-74.90122157760001</v>
+        <v>-76.63450767719999</v>
       </c>
       <c r="P58">
-        <v>-438.1208440224001</v>
+        <v>-448.2593805228</v>
       </c>
       <c r="Q58">
-        <v>-321.4208440224001</v>
+        <v>-331.5593805228</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1253784684659029</v>
+        <v>0.1272291305232495</v>
       </c>
       <c r="T58">
-        <v>1.83783991838113</v>
+        <v>1.880580381599296</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.03333643864542633</v>
+        <v>0.03275158884462938</v>
       </c>
       <c r="W58">
-        <v>0.2279392677674085</v>
+        <v>0.2280771753504364</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.2283317715440158</v>
+        <v>0.2243259509906123</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.184712516074746</v>
+        <v>0.186612516074746</v>
       </c>
       <c r="C59">
-        <v>-1510.880553716499</v>
+        <v>-1578.273767928078</v>
       </c>
       <c r="D59">
-        <v>1281.4984462835</v>
+        <v>1264.452232071922</v>
       </c>
       <c r="E59">
-        <v>1923.679</v>
+        <v>1974.026</v>
       </c>
       <c r="F59">
-        <v>2869.779</v>
+        <v>2920.126</v>
       </c>
       <c r="G59">
         <v>77.40000000000001</v>
@@ -6131,37 +6131,37 @@
         <v>151.8</v>
       </c>
       <c r="M59">
-        <v>676.6938882000001</v>
+        <v>688.5657108</v>
       </c>
       <c r="N59">
-        <v>-524.8938882</v>
+        <v>-536.7657108000001</v>
       </c>
       <c r="O59">
-        <v>-76.63450767719999</v>
+        <v>-78.36779377680001</v>
       </c>
       <c r="P59">
-        <v>-448.2593805228</v>
+        <v>-458.3979170232001</v>
       </c>
       <c r="Q59">
-        <v>-331.5593805228</v>
+        <v>-341.6979170232001</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1272291305232495</v>
+        <v>0.1291679193452316</v>
       </c>
       <c r="T59">
-        <v>1.880580381599296</v>
+        <v>1.925356104970708</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.03275158884462938</v>
+        <v>0.03218690627834266</v>
       </c>
       <c r="W59">
-        <v>0.2280771753504364</v>
+        <v>0.2282103274995668</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.2243259509906123</v>
+        <v>0.2204582621804292</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.186612516074746</v>
+        <v>0.188512516074746</v>
       </c>
       <c r="C60">
-        <v>-1578.273767928078</v>
+        <v>-1645.219445096401</v>
       </c>
       <c r="D60">
-        <v>1264.452232071922</v>
+        <v>1247.853554903599</v>
       </c>
       <c r="E60">
-        <v>1974.026</v>
+        <v>2024.373</v>
       </c>
       <c r="F60">
-        <v>2920.126</v>
+        <v>2970.473</v>
       </c>
       <c r="G60">
         <v>77.40000000000001</v>
@@ -6213,37 +6213,37 @@
         <v>151.8</v>
       </c>
       <c r="M60">
-        <v>688.5657107999999</v>
+        <v>700.4375334</v>
       </c>
       <c r="N60">
-        <v>-536.7657107999999</v>
+        <v>-548.6375333999999</v>
       </c>
       <c r="O60">
-        <v>-78.36779377679997</v>
+        <v>-80.10107987639999</v>
       </c>
       <c r="P60">
-        <v>-458.3979170231999</v>
+        <v>-468.5364535236</v>
       </c>
       <c r="Q60">
-        <v>-341.6979170231999</v>
+        <v>-351.8364535236</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1291679193452316</v>
+        <v>0.1312012832317007</v>
       </c>
       <c r="T60">
-        <v>1.925356104970708</v>
+        <v>1.972316009969993</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.03218690627834267</v>
+        <v>0.03164136549396397</v>
       </c>
       <c r="W60">
-        <v>0.2282103274995668</v>
+        <v>0.2283389660165233</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.2204582621804293</v>
+        <v>0.2167216814655067</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.188512516074746</v>
+        <v>0.190412516074746</v>
       </c>
       <c r="C61">
-        <v>-1645.219445096401</v>
+        <v>-1711.734981539244</v>
       </c>
       <c r="D61">
-        <v>1247.853554903599</v>
+        <v>1231.685018460755</v>
       </c>
       <c r="E61">
-        <v>2024.373</v>
+        <v>2074.72</v>
       </c>
       <c r="F61">
-        <v>2970.473</v>
+        <v>3020.82</v>
       </c>
       <c r="G61">
         <v>77.40000000000001</v>
@@ -6295,37 +6295,37 @@
         <v>151.8</v>
       </c>
       <c r="M61">
-        <v>700.4375334</v>
+        <v>712.309356</v>
       </c>
       <c r="N61">
-        <v>-548.6375333999999</v>
+        <v>-560.509356</v>
       </c>
       <c r="O61">
-        <v>-80.10107987639999</v>
+        <v>-81.834365976</v>
       </c>
       <c r="P61">
-        <v>-468.5364535236</v>
+        <v>-478.674990024</v>
       </c>
       <c r="Q61">
-        <v>-351.8364535236</v>
+        <v>-361.974990024</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1312012832317007</v>
+        <v>0.1333363153124932</v>
       </c>
       <c r="T61">
-        <v>1.972316009969993</v>
+        <v>2.021623910219243</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.03164136549396397</v>
+        <v>0.03111400940239791</v>
       </c>
       <c r="W61">
-        <v>0.2283389660165233</v>
+        <v>0.2284633165829146</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.2167216814655067</v>
+        <v>0.2131096534410816</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.190412516074746</v>
+        <v>0.1923125160747461</v>
       </c>
       <c r="C62">
-        <v>-1711.734981539244</v>
+        <v>-1777.836883485519</v>
       </c>
       <c r="D62">
-        <v>1231.685018460755</v>
+        <v>1215.930116514481</v>
       </c>
       <c r="E62">
-        <v>2074.72</v>
+        <v>2125.067</v>
       </c>
       <c r="F62">
-        <v>3020.82</v>
+        <v>3071.167</v>
       </c>
       <c r="G62">
         <v>77.40000000000001</v>
@@ -6377,37 +6377,37 @@
         <v>151.8</v>
       </c>
       <c r="M62">
-        <v>712.309356</v>
+        <v>724.1811786</v>
       </c>
       <c r="N62">
-        <v>-560.509356</v>
+        <v>-572.3811785999999</v>
       </c>
       <c r="O62">
-        <v>-81.834365976</v>
+        <v>-83.56765207559998</v>
       </c>
       <c r="P62">
-        <v>-478.674990024</v>
+        <v>-488.8135265243999</v>
       </c>
       <c r="Q62">
-        <v>-361.974990024</v>
+        <v>-372.1135265243999</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1333363153124932</v>
+        <v>0.1355808362179418</v>
       </c>
       <c r="T62">
-        <v>2.021623910219243</v>
+        <v>2.073460420737685</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.03111400940239791</v>
+        <v>0.03060394367448975</v>
       </c>
       <c r="W62">
-        <v>0.2284633165829146</v>
+        <v>0.2285835900815553</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.2131096534410816</v>
+        <v>0.2096160525649984</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1923125160747461</v>
+        <v>0.194212516074746</v>
       </c>
       <c r="C63">
-        <v>-1777.836883485519</v>
+        <v>-1843.540823283434</v>
       </c>
       <c r="D63">
-        <v>1215.930116514481</v>
+        <v>1200.573176716566</v>
       </c>
       <c r="E63">
-        <v>2125.067</v>
+        <v>2175.414</v>
       </c>
       <c r="F63">
-        <v>3071.167</v>
+        <v>3121.514</v>
       </c>
       <c r="G63">
         <v>77.40000000000001</v>
@@ -6459,37 +6459,37 @@
         <v>151.8</v>
       </c>
       <c r="M63">
-        <v>724.1811786</v>
+        <v>736.0530011999999</v>
       </c>
       <c r="N63">
-        <v>-572.3811785999999</v>
+        <v>-584.2530012</v>
       </c>
       <c r="O63">
-        <v>-83.56765207559998</v>
+        <v>-85.30093817519999</v>
       </c>
       <c r="P63">
-        <v>-488.8135265243999</v>
+        <v>-498.9520630248</v>
       </c>
       <c r="Q63">
-        <v>-372.1135265243999</v>
+        <v>-382.2520630248</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1355808362179418</v>
+        <v>0.1379434898026244</v>
       </c>
       <c r="T63">
-        <v>2.073460420737685</v>
+        <v>2.128025168651835</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.03060394367448975</v>
+        <v>0.03011033167973992</v>
       </c>
       <c r="W63">
-        <v>0.2285835900815553</v>
+        <v>0.2286999837899173</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.2096160525649984</v>
+        <v>0.2062351484913693</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.194212516074746</v>
+        <v>0.1961125160747461</v>
       </c>
       <c r="C64">
-        <v>-1843.540823283434</v>
+        <v>-1908.861691402413</v>
       </c>
       <c r="D64">
-        <v>1200.573176716566</v>
+        <v>1185.599308597586</v>
       </c>
       <c r="E64">
-        <v>2175.414</v>
+        <v>2225.761</v>
       </c>
       <c r="F64">
-        <v>3121.514</v>
+        <v>3171.861</v>
       </c>
       <c r="G64">
         <v>77.40000000000001</v>
@@ -6541,37 +6541,37 @@
         <v>151.8</v>
       </c>
       <c r="M64">
-        <v>736.0530011999999</v>
+        <v>747.9248238</v>
       </c>
       <c r="N64">
-        <v>-584.2530012</v>
+        <v>-596.1248238000001</v>
       </c>
       <c r="O64">
-        <v>-85.30093817519999</v>
+        <v>-87.0342242748</v>
       </c>
       <c r="P64">
-        <v>-498.9520630248</v>
+        <v>-509.0905995252</v>
       </c>
       <c r="Q64">
-        <v>-382.2520630248</v>
+        <v>-392.3905995252001</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1379434898026244</v>
+        <v>0.1404338543918845</v>
       </c>
       <c r="T64">
-        <v>2.128025168651835</v>
+        <v>2.185539362399181</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.03011033167973992</v>
+        <v>0.02963238990704563</v>
       </c>
       <c r="W64">
-        <v>0.2286999837899173</v>
+        <v>0.2288126824599186</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.2062351484913693</v>
+        <v>0.2029615747057919</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1961125160747461</v>
+        <v>0.198012516074746</v>
       </c>
       <c r="C65">
-        <v>-1908.861691402413</v>
+        <v>-1973.813644591449</v>
       </c>
       <c r="D65">
-        <v>1185.599308597586</v>
+        <v>1170.994355408551</v>
       </c>
       <c r="E65">
-        <v>2225.761</v>
+        <v>2276.108</v>
       </c>
       <c r="F65">
-        <v>3171.861</v>
+        <v>3222.208</v>
       </c>
       <c r="G65">
         <v>77.40000000000001</v>
@@ -6623,37 +6623,37 @@
         <v>151.8</v>
       </c>
       <c r="M65">
-        <v>747.9248238</v>
+        <v>759.7966464000001</v>
       </c>
       <c r="N65">
-        <v>-596.1248238000001</v>
+        <v>-607.9966464000001</v>
       </c>
       <c r="O65">
-        <v>-87.0342242748</v>
+        <v>-88.76751037440002</v>
       </c>
       <c r="P65">
-        <v>-509.0905995252</v>
+        <v>-519.2291360256002</v>
       </c>
       <c r="Q65">
-        <v>-392.3905995252001</v>
+        <v>-402.5291360256002</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1404338543918845</v>
+        <v>0.1430625725694369</v>
       </c>
       <c r="T65">
-        <v>2.185539362399181</v>
+        <v>2.246248789132492</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.02963238990704563</v>
+        <v>0.02916938381474804</v>
       </c>
       <c r="W65">
-        <v>0.2288126824599186</v>
+        <v>0.2289218592964824</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.2029615747057919</v>
+        <v>0.1997903001010138</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.198012516074746</v>
+        <v>0.199912516074746</v>
       </c>
       <c r="C66">
-        <v>-1973.813644591449</v>
+        <v>-2038.410150521304</v>
       </c>
       <c r="D66">
-        <v>1170.994355408551</v>
+        <v>1156.744849478695</v>
       </c>
       <c r="E66">
-        <v>2276.108</v>
+        <v>2326.455</v>
       </c>
       <c r="F66">
-        <v>3222.208</v>
+        <v>3272.555</v>
       </c>
       <c r="G66">
         <v>77.40000000000001</v>
@@ -6705,37 +6705,37 @@
         <v>151.8</v>
       </c>
       <c r="M66">
-        <v>759.7966464000001</v>
+        <v>771.668469</v>
       </c>
       <c r="N66">
-        <v>-607.9966464000001</v>
+        <v>-619.868469</v>
       </c>
       <c r="O66">
-        <v>-88.76751037440002</v>
+        <v>-90.500796474</v>
       </c>
       <c r="P66">
-        <v>-519.2291360256002</v>
+        <v>-529.367672526</v>
       </c>
       <c r="Q66">
-        <v>-402.5291360256002</v>
+        <v>-412.667672526</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1430625725694369</v>
+        <v>0.145841503214278</v>
       </c>
       <c r="T66">
-        <v>2.246248789132492</v>
+        <v>2.310427325964849</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.02916938381474804</v>
+        <v>0.02872062406375192</v>
       </c>
       <c r="W66">
-        <v>0.2289218592964824</v>
+        <v>0.2290276768457673</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.1997903001010138</v>
+        <v>0.196716603176383</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.199912516074746</v>
+        <v>0.201812516074746</v>
       </c>
       <c r="C67">
-        <v>-2038.410150521304</v>
+        <v>-2102.664029206476</v>
       </c>
       <c r="D67">
-        <v>1156.744849478695</v>
+        <v>1142.837970793524</v>
       </c>
       <c r="E67">
-        <v>2326.455</v>
+        <v>2376.802</v>
       </c>
       <c r="F67">
-        <v>3272.555</v>
+        <v>3322.902</v>
       </c>
       <c r="G67">
         <v>77.40000000000001</v>
@@ -6787,37 +6787,37 @@
         <v>151.8</v>
       </c>
       <c r="M67">
-        <v>771.668469</v>
+        <v>783.5402916</v>
       </c>
       <c r="N67">
-        <v>-619.868469</v>
+        <v>-631.7402916000001</v>
       </c>
       <c r="O67">
-        <v>-90.500796474</v>
+        <v>-92.23408257360001</v>
       </c>
       <c r="P67">
-        <v>-529.367672526</v>
+        <v>-539.5062090264</v>
       </c>
       <c r="Q67">
-        <v>-412.667672526</v>
+        <v>-422.8062090264</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.145841503214278</v>
+        <v>0.1487839003676391</v>
       </c>
       <c r="T67">
-        <v>2.310427325964849</v>
+        <v>2.378381070846169</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.02872062406375192</v>
+        <v>0.02828546309308901</v>
       </c>
       <c r="W67">
-        <v>0.2290276768457673</v>
+        <v>0.2291302878026496</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.196716603176383</v>
+        <v>0.1937360485828014</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.201812516074746</v>
+        <v>0.2037125160747461</v>
       </c>
       <c r="C68">
-        <v>-2102.664029206476</v>
+        <v>-2166.587491474686</v>
       </c>
       <c r="D68">
-        <v>1142.837970793524</v>
+        <v>1129.261508525314</v>
       </c>
       <c r="E68">
-        <v>2376.802</v>
+        <v>2427.149</v>
       </c>
       <c r="F68">
-        <v>3322.902</v>
+        <v>3373.249</v>
       </c>
       <c r="G68">
         <v>77.40000000000001</v>
@@ -6869,37 +6869,37 @@
         <v>151.8</v>
       </c>
       <c r="M68">
-        <v>783.5402916</v>
+        <v>795.4121142000001</v>
       </c>
       <c r="N68">
-        <v>-631.7402916000001</v>
+        <v>-643.6121142000002</v>
       </c>
       <c r="O68">
-        <v>-92.23408257360001</v>
+        <v>-93.96736867320001</v>
       </c>
       <c r="P68">
-        <v>-539.5062090264</v>
+        <v>-549.6447455268002</v>
       </c>
       <c r="Q68">
-        <v>-422.8062090264</v>
+        <v>-432.9447455268002</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1487839003676391</v>
+        <v>0.1519046246212039</v>
       </c>
       <c r="T68">
-        <v>2.378381070846169</v>
+        <v>2.450453224508174</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.02828546309308901</v>
+        <v>0.02786329200214738</v>
       </c>
       <c r="W68">
-        <v>0.2291302878026496</v>
+        <v>0.2292298357458937</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.1937360485828014</v>
+        <v>0.1908444657681326</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2037125160747461</v>
+        <v>0.205612516074746</v>
       </c>
       <c r="C69">
-        <v>-2166.587491474686</v>
+        <v>-2230.192174726567</v>
       </c>
       <c r="D69">
-        <v>1129.261508525314</v>
+        <v>1116.003825273433</v>
       </c>
       <c r="E69">
-        <v>2427.149</v>
+        <v>2477.496</v>
       </c>
       <c r="F69">
-        <v>3373.249</v>
+        <v>3423.596</v>
       </c>
       <c r="G69">
         <v>77.40000000000001</v>
@@ -6951,37 +6951,37 @@
         <v>151.8</v>
       </c>
       <c r="M69">
-        <v>795.4121142000001</v>
+        <v>807.2839368</v>
       </c>
       <c r="N69">
-        <v>-643.6121142000002</v>
+        <v>-655.4839368</v>
       </c>
       <c r="O69">
-        <v>-93.96736867320001</v>
+        <v>-95.70065477279999</v>
       </c>
       <c r="P69">
-        <v>-549.6447455268002</v>
+        <v>-559.7832820272</v>
       </c>
       <c r="Q69">
-        <v>-432.9447455268002</v>
+        <v>-443.0832820272</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1519046246212039</v>
+        <v>0.1552203941406165</v>
       </c>
       <c r="T69">
-        <v>2.450453224508174</v>
+        <v>2.527029887774054</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.02786329200214738</v>
+        <v>0.02745353770799816</v>
       </c>
       <c r="W69">
-        <v>0.2292298357458937</v>
+        <v>0.229326455808454</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.1908444657681326</v>
+        <v>0.1880379295068366</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.205612516074746</v>
+        <v>0.207512516074746</v>
       </c>
       <c r="C70">
-        <v>-2230.192174726567</v>
+        <v>-2293.489176205623</v>
       </c>
       <c r="D70">
-        <v>1116.003825273433</v>
+        <v>1103.053823794377</v>
       </c>
       <c r="E70">
-        <v>2477.496</v>
+        <v>2527.843</v>
       </c>
       <c r="F70">
-        <v>3423.596</v>
+        <v>3473.943</v>
       </c>
       <c r="G70">
         <v>77.40000000000001</v>
@@ -7033,37 +7033,37 @@
         <v>151.8</v>
       </c>
       <c r="M70">
-        <v>807.2839368</v>
+        <v>819.1557594000001</v>
       </c>
       <c r="N70">
-        <v>-655.4839368</v>
+        <v>-667.3557594000001</v>
       </c>
       <c r="O70">
-        <v>-95.70065477279999</v>
+        <v>-97.43394087240002</v>
       </c>
       <c r="P70">
-        <v>-559.7832820272</v>
+        <v>-569.9218185276001</v>
       </c>
       <c r="Q70">
-        <v>-443.0832820272</v>
+        <v>-453.2218185276001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1552203941406165</v>
+        <v>0.1587500842741848</v>
       </c>
       <c r="T70">
-        <v>2.527029887774054</v>
+        <v>2.608546980928056</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.02745353770799816</v>
+        <v>0.02705566034991122</v>
       </c>
       <c r="W70">
-        <v>0.229326455808454</v>
+        <v>0.2294202752894909</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.1880379295068366</v>
+        <v>0.1853127421226796</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.207512516074746</v>
+        <v>0.2094125160747461</v>
       </c>
       <c r="C71">
-        <v>-2293.489176205623</v>
+        <v>-2356.489083978393</v>
       </c>
       <c r="D71">
-        <v>1103.053823794377</v>
+        <v>1090.400916021607</v>
       </c>
       <c r="E71">
-        <v>2527.843</v>
+        <v>2578.190000000001</v>
       </c>
       <c r="F71">
-        <v>3473.943</v>
+        <v>3524.29</v>
       </c>
       <c r="G71">
         <v>77.40000000000001</v>
@@ -7115,37 +7115,37 @@
         <v>151.8</v>
       </c>
       <c r="M71">
-        <v>819.1557594000001</v>
+        <v>831.0275820000002</v>
       </c>
       <c r="N71">
-        <v>-667.3557594000001</v>
+        <v>-679.2275820000002</v>
       </c>
       <c r="O71">
-        <v>-97.43394087240002</v>
+        <v>-99.16722697200002</v>
       </c>
       <c r="P71">
-        <v>-569.9218185276001</v>
+        <v>-580.0603550280002</v>
       </c>
       <c r="Q71">
-        <v>-453.2218185276001</v>
+        <v>-463.3603550280002</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1587500842741848</v>
+        <v>0.1625150870833243</v>
       </c>
       <c r="T71">
-        <v>2.608546980928056</v>
+        <v>2.695498546958991</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.02705566034991122</v>
+        <v>0.02666915091634106</v>
       </c>
       <c r="W71">
-        <v>0.2294202752894909</v>
+        <v>0.2295114142139268</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.1853127421226796</v>
+        <v>0.1826654172352127</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2094125160747461</v>
+        <v>0.211312516074746</v>
       </c>
       <c r="C72">
-        <v>-2356.489083978393</v>
+        <v>-2419.2020058066</v>
       </c>
       <c r="D72">
-        <v>1090.400916021607</v>
+        <v>1078.0349941934</v>
       </c>
       <c r="E72">
-        <v>2578.190000000001</v>
+        <v>2628.537</v>
       </c>
       <c r="F72">
-        <v>3524.29</v>
+        <v>3574.637</v>
       </c>
       <c r="G72">
         <v>77.40000000000001</v>
@@ -7197,37 +7197,37 @@
         <v>151.8</v>
       </c>
       <c r="M72">
-        <v>831.0275820000002</v>
+        <v>842.8994046</v>
       </c>
       <c r="N72">
-        <v>-679.2275820000002</v>
+        <v>-691.0994046000001</v>
       </c>
       <c r="O72">
-        <v>-99.16722697200002</v>
+        <v>-100.9005130716</v>
       </c>
       <c r="P72">
-        <v>-580.0603550280002</v>
+        <v>-590.1988915284001</v>
       </c>
       <c r="Q72">
-        <v>-463.3603550280002</v>
+        <v>-473.4988915284001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1625150870833243</v>
+        <v>0.1665397452586114</v>
       </c>
       <c r="T72">
-        <v>2.695498546958991</v>
+        <v>2.788446772716198</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.02666915091634106</v>
+        <v>0.02629352907244894</v>
       </c>
       <c r="W72">
-        <v>0.2295114142139268</v>
+        <v>0.2295999858447166</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.1826654172352127</v>
+        <v>0.1800926648797871</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.211312516074746</v>
+        <v>0.213212516074746</v>
       </c>
       <c r="C73">
-        <v>-2419.2020058066</v>
+        <v>-2481.637596076743</v>
       </c>
       <c r="D73">
-        <v>1078.0349941934</v>
+        <v>1065.946403923257</v>
       </c>
       <c r="E73">
-        <v>2628.537</v>
+        <v>2678.884</v>
       </c>
       <c r="F73">
-        <v>3574.637</v>
+        <v>3624.984</v>
       </c>
       <c r="G73">
         <v>77.40000000000001</v>
@@ -7279,37 +7279,37 @@
         <v>151.8</v>
       </c>
       <c r="M73">
-        <v>842.8994045999999</v>
+        <v>854.7712272</v>
       </c>
       <c r="N73">
-        <v>-691.0994045999998</v>
+        <v>-702.9712271999999</v>
       </c>
       <c r="O73">
-        <v>-100.9005130716</v>
+        <v>-102.6337991712</v>
       </c>
       <c r="P73">
-        <v>-590.1988915283998</v>
+        <v>-600.3374280288</v>
       </c>
       <c r="Q73">
-        <v>-473.4988915283998</v>
+        <v>-483.6374280288</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1665397452586113</v>
+        <v>0.1708518790178475</v>
       </c>
       <c r="T73">
-        <v>2.788446772716197</v>
+        <v>2.888034157456061</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.02629352907244894</v>
+        <v>0.02592834116866492</v>
       </c>
       <c r="W73">
-        <v>0.2295999858447166</v>
+        <v>0.2296860971524288</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.1800926648797874</v>
+        <v>0.1775913778675681</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.213212516074746</v>
+        <v>0.215112516074746</v>
       </c>
       <c r="C74">
-        <v>-2481.637596076743</v>
+        <v>-2543.805080937918</v>
       </c>
       <c r="D74">
-        <v>1065.946403923257</v>
+        <v>1054.125919062081</v>
       </c>
       <c r="E74">
-        <v>2678.884</v>
+        <v>2729.231</v>
       </c>
       <c r="F74">
-        <v>3624.984</v>
+        <v>3675.331</v>
       </c>
       <c r="G74">
         <v>77.40000000000001</v>
@@ -7361,37 +7361,37 @@
         <v>151.8</v>
       </c>
       <c r="M74">
-        <v>854.7712272</v>
+        <v>866.6430498</v>
       </c>
       <c r="N74">
-        <v>-702.9712271999999</v>
+        <v>-714.8430498</v>
       </c>
       <c r="O74">
-        <v>-102.6337991712</v>
+        <v>-104.3670852708</v>
       </c>
       <c r="P74">
-        <v>-600.3374280288</v>
+        <v>-610.4759645292</v>
       </c>
       <c r="Q74">
-        <v>-483.6374280288</v>
+        <v>-493.7759645292001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1708518790178475</v>
+        <v>0.1754834300925825</v>
       </c>
       <c r="T74">
-        <v>2.888034157456061</v>
+        <v>2.994998385509989</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.02592834116866492</v>
+        <v>0.02557315841292979</v>
       </c>
       <c r="W74">
-        <v>0.2296860971524288</v>
+        <v>0.2297698492462311</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.1775913778675681</v>
+        <v>0.1751586192666423</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.215112516074746</v>
+        <v>0.217012516074746</v>
       </c>
       <c r="C75">
-        <v>-2543.805080937918</v>
+        <v>-2605.713281785441</v>
       </c>
       <c r="D75">
-        <v>1054.125919062081</v>
+        <v>1042.564718214559</v>
       </c>
       <c r="E75">
-        <v>2729.231</v>
+        <v>2779.578</v>
       </c>
       <c r="F75">
-        <v>3675.331</v>
+        <v>3725.678</v>
       </c>
       <c r="G75">
         <v>77.40000000000001</v>
@@ -7443,37 +7443,37 @@
         <v>151.8</v>
       </c>
       <c r="M75">
-        <v>866.6430498</v>
+        <v>878.5148724000001</v>
       </c>
       <c r="N75">
-        <v>-714.8430498</v>
+        <v>-726.7148724000001</v>
       </c>
       <c r="O75">
-        <v>-104.3670852708</v>
+        <v>-106.1003713704</v>
       </c>
       <c r="P75">
-        <v>-610.4759645292</v>
+        <v>-620.6145010296001</v>
       </c>
       <c r="Q75">
-        <v>-493.7759645292001</v>
+        <v>-503.9145010296001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1754834300925825</v>
+        <v>0.1804712543269126</v>
       </c>
       <c r="T75">
-        <v>2.994998385509989</v>
+        <v>3.110190631106527</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.02557315841292979</v>
+        <v>0.02522757519113344</v>
       </c>
       <c r="W75">
-        <v>0.2297698492462311</v>
+        <v>0.2298513377699307</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.1751586192666423</v>
+        <v>0.1727916108981742</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.217012516074746</v>
+        <v>0.218912516074746</v>
       </c>
       <c r="C76">
-        <v>-2605.713281785441</v>
+        <v>-2667.370637215879</v>
       </c>
       <c r="D76">
-        <v>1042.564718214559</v>
+        <v>1031.25436278412</v>
       </c>
       <c r="E76">
-        <v>2779.578</v>
+        <v>2829.925</v>
       </c>
       <c r="F76">
-        <v>3725.678</v>
+        <v>3776.025</v>
       </c>
       <c r="G76">
         <v>77.40000000000001</v>
@@ -7525,37 +7525,37 @@
         <v>151.8</v>
       </c>
       <c r="M76">
-        <v>878.5148724000001</v>
+        <v>890.3866949999999</v>
       </c>
       <c r="N76">
-        <v>-726.7148724000001</v>
+        <v>-738.586695</v>
       </c>
       <c r="O76">
-        <v>-106.1003713704</v>
+        <v>-107.83365747</v>
       </c>
       <c r="P76">
-        <v>-620.6145010296001</v>
+        <v>-630.75303753</v>
       </c>
       <c r="Q76">
-        <v>-503.9145010296001</v>
+        <v>-514.05303753</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1804712543269126</v>
+        <v>0.1858581044999892</v>
       </c>
       <c r="T76">
-        <v>3.110190631106527</v>
+        <v>3.234598256350789</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.02522757519113344</v>
+        <v>0.02489120752191833</v>
       </c>
       <c r="W76">
-        <v>0.2298513377699307</v>
+        <v>0.2299306532663317</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.1727916108981742</v>
+        <v>0.1704877227528653</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.218912516074746</v>
+        <v>0.220812516074746</v>
       </c>
       <c r="C77">
-        <v>-2667.370637215879</v>
+        <v>-2728.785223568347</v>
       </c>
       <c r="D77">
-        <v>1031.25436278412</v>
+        <v>1020.186776431653</v>
       </c>
       <c r="E77">
-        <v>2829.925</v>
+        <v>2880.272</v>
       </c>
       <c r="F77">
-        <v>3776.025</v>
+        <v>3826.372</v>
       </c>
       <c r="G77">
         <v>77.40000000000001</v>
@@ -7607,37 +7607,37 @@
         <v>151.8</v>
       </c>
       <c r="M77">
-        <v>890.3866949999999</v>
+        <v>902.2585176</v>
       </c>
       <c r="N77">
-        <v>-738.586695</v>
+        <v>-750.4585176000001</v>
       </c>
       <c r="O77">
-        <v>-107.83365747</v>
+        <v>-109.5669435696</v>
       </c>
       <c r="P77">
-        <v>-630.75303753</v>
+        <v>-640.8915740304001</v>
       </c>
       <c r="Q77">
-        <v>-514.05303753</v>
+        <v>-524.1915740304</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1858581044999892</v>
+        <v>0.1916938588541554</v>
       </c>
       <c r="T77">
-        <v>3.234598256350789</v>
+        <v>3.369373183698738</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.02489120752191833</v>
+        <v>0.02456369163347203</v>
       </c>
       <c r="W77">
-        <v>0.2299306532663317</v>
+        <v>0.2300078815128273</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.1704877227528653</v>
+        <v>0.1682444632429591</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.220812516074746</v>
+        <v>0.2227125160747461</v>
       </c>
       <c r="C78">
-        <v>-2728.785223568347</v>
+        <v>-2789.964774157113</v>
       </c>
       <c r="D78">
-        <v>1020.186776431653</v>
+        <v>1009.354225842887</v>
       </c>
       <c r="E78">
-        <v>2880.272</v>
+        <v>2930.619</v>
       </c>
       <c r="F78">
-        <v>3826.372</v>
+        <v>3876.719</v>
       </c>
       <c r="G78">
         <v>77.40000000000001</v>
@@ -7689,37 +7689,37 @@
         <v>151.8</v>
       </c>
       <c r="M78">
-        <v>902.2585176</v>
+        <v>914.1303402000001</v>
       </c>
       <c r="N78">
-        <v>-750.4585176000001</v>
+        <v>-762.3303402000001</v>
       </c>
       <c r="O78">
-        <v>-109.5669435696</v>
+        <v>-111.3002296692</v>
       </c>
       <c r="P78">
-        <v>-640.8915740304001</v>
+        <v>-651.0301105308001</v>
       </c>
       <c r="Q78">
-        <v>-524.1915740304</v>
+        <v>-534.3301105308001</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1916938588541554</v>
+        <v>0.1980370701086838</v>
       </c>
       <c r="T78">
-        <v>3.369373183698738</v>
+        <v>3.515867669946509</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.02456369163347203</v>
+        <v>0.02424468265121915</v>
       </c>
       <c r="W78">
-        <v>0.2300078815128273</v>
+        <v>0.2300831038308425</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.1682444632429591</v>
+        <v>0.1660594702138297</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2227125160747461</v>
+        <v>0.224612516074746</v>
       </c>
       <c r="C79">
-        <v>-2789.964774157113</v>
+        <v>-2850.916697291799</v>
       </c>
       <c r="D79">
-        <v>1009.354225842887</v>
+        <v>998.7493027082006</v>
       </c>
       <c r="E79">
-        <v>2930.619</v>
+        <v>2980.966</v>
       </c>
       <c r="F79">
-        <v>3876.719</v>
+        <v>3927.066</v>
       </c>
       <c r="G79">
         <v>77.40000000000001</v>
@@ -7771,37 +7771,37 @@
         <v>151.8</v>
       </c>
       <c r="M79">
-        <v>914.1303402000001</v>
+        <v>926.0021628</v>
       </c>
       <c r="N79">
-        <v>-762.3303402000001</v>
+        <v>-774.2021628</v>
       </c>
       <c r="O79">
-        <v>-111.3002296692</v>
+        <v>-113.0335157688</v>
       </c>
       <c r="P79">
-        <v>-651.0301105308001</v>
+        <v>-661.1686470312</v>
       </c>
       <c r="Q79">
-        <v>-534.3301105308001</v>
+        <v>-544.4686470311999</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1980370701086838</v>
+        <v>0.2049569369318059</v>
       </c>
       <c r="T79">
-        <v>3.515867669946509</v>
+        <v>3.67567983676226</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.02424468265121915</v>
+        <v>0.02393385338645993</v>
       </c>
       <c r="W79">
-        <v>0.2300831038308425</v>
+        <v>0.2301563973714728</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.1660594702138297</v>
+        <v>0.1639305026469858</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.224612516074746</v>
+        <v>0.2265125160747461</v>
       </c>
       <c r="C80">
-        <v>-2850.916697291799</v>
+        <v>-2911.648093173399</v>
       </c>
       <c r="D80">
-        <v>998.7493027082006</v>
+        <v>988.3649068266014</v>
       </c>
       <c r="E80">
-        <v>2980.966</v>
+        <v>3031.313</v>
       </c>
       <c r="F80">
-        <v>3927.066</v>
+        <v>3977.413</v>
       </c>
       <c r="G80">
         <v>77.40000000000001</v>
@@ -7853,37 +7853,37 @@
         <v>151.8</v>
       </c>
       <c r="M80">
-        <v>926.0021628</v>
+        <v>937.8739854</v>
       </c>
       <c r="N80">
-        <v>-774.2021628</v>
+        <v>-786.0739854000001</v>
       </c>
       <c r="O80">
-        <v>-113.0335157688</v>
+        <v>-114.7668018684</v>
       </c>
       <c r="P80">
-        <v>-661.1686470312</v>
+        <v>-671.3071835316001</v>
       </c>
       <c r="Q80">
-        <v>-544.4686470311999</v>
+        <v>-554.6071835316001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2049569369318059</v>
+        <v>0.2125358386904633</v>
       </c>
       <c r="T80">
-        <v>3.67567983676226</v>
+        <v>3.850712209941415</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.02393385338645993</v>
+        <v>0.02363089321701107</v>
       </c>
       <c r="W80">
-        <v>0.2301563973714728</v>
+        <v>0.2302278353794288</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.1639305026469858</v>
+        <v>0.1618554329932265</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2265125160747461</v>
+        <v>0.2284125160747461</v>
       </c>
       <c r="C81">
-        <v>-2911.648093173399</v>
+        <v>-2972.165769747088</v>
       </c>
       <c r="D81">
-        <v>988.3649068266014</v>
+        <v>978.1942302529125</v>
       </c>
       <c r="E81">
-        <v>3031.313</v>
+        <v>3081.66</v>
       </c>
       <c r="F81">
-        <v>3977.413</v>
+        <v>4027.76</v>
       </c>
       <c r="G81">
         <v>77.40000000000001</v>
@@ -7935,37 +7935,37 @@
         <v>151.8</v>
       </c>
       <c r="M81">
-        <v>937.8739854</v>
+        <v>949.7458080000001</v>
       </c>
       <c r="N81">
-        <v>-786.0739854000001</v>
+        <v>-797.9458080000002</v>
       </c>
       <c r="O81">
-        <v>-114.7668018684</v>
+        <v>-116.500087968</v>
       </c>
       <c r="P81">
-        <v>-671.3071835316001</v>
+        <v>-681.4457200320002</v>
       </c>
       <c r="Q81">
-        <v>-554.6071835316001</v>
+        <v>-564.7457200320001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2125358386904633</v>
+        <v>0.2208726306249864</v>
       </c>
       <c r="T81">
-        <v>3.850712209941415</v>
+        <v>4.043247820438486</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.02363089321701107</v>
+        <v>0.02333550705179843</v>
       </c>
       <c r="W81">
-        <v>0.2302278353794288</v>
+        <v>0.2302974874371859</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.1618554329932265</v>
+        <v>0.1598322400808111</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2284125160747461</v>
+        <v>0.2303125160747461</v>
       </c>
       <c r="C82">
-        <v>-2972.165769747088</v>
+        <v>-3032.476257586221</v>
       </c>
       <c r="D82">
-        <v>978.1942302529125</v>
+        <v>968.2307424137791</v>
       </c>
       <c r="E82">
-        <v>3081.66</v>
+        <v>3132.007</v>
       </c>
       <c r="F82">
-        <v>4027.76</v>
+        <v>4078.107</v>
       </c>
       <c r="G82">
         <v>77.40000000000001</v>
@@ -8017,37 +8017,37 @@
         <v>151.8</v>
       </c>
       <c r="M82">
-        <v>949.7458080000001</v>
+        <v>961.6176306</v>
       </c>
       <c r="N82">
-        <v>-797.9458080000002</v>
+        <v>-809.8176306</v>
       </c>
       <c r="O82">
-        <v>-116.500087968</v>
+        <v>-118.2333740676</v>
       </c>
       <c r="P82">
-        <v>-681.4457200320002</v>
+        <v>-691.5842565324</v>
       </c>
       <c r="Q82">
-        <v>-564.7457200320001</v>
+        <v>-574.8842565323999</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2208726306249864</v>
+        <v>0.2300869796052489</v>
       </c>
       <c r="T82">
-        <v>4.043247820438486</v>
+        <v>4.25605033730367</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.02333550705179843</v>
+        <v>0.0230474143721466</v>
       </c>
       <c r="W82">
-        <v>0.2302974874371859</v>
+        <v>0.2303654196910478</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.1598322400808111</v>
+        <v>0.1578590025489492</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2303125160747461</v>
+        <v>0.2322125160747461</v>
       </c>
       <c r="C83">
-        <v>-3032.476257586221</v>
+        <v>-3092.585823875883</v>
       </c>
       <c r="D83">
-        <v>968.2307424137791</v>
+        <v>958.4681761241168</v>
       </c>
       <c r="E83">
-        <v>3132.007</v>
+        <v>3182.354</v>
       </c>
       <c r="F83">
-        <v>4078.107</v>
+        <v>4128.454</v>
       </c>
       <c r="G83">
         <v>77.40000000000001</v>
@@ -8099,37 +8099,37 @@
         <v>151.8</v>
       </c>
       <c r="M83">
-        <v>961.6176306</v>
+        <v>973.4894532</v>
       </c>
       <c r="N83">
-        <v>-809.8176306</v>
+        <v>-821.6894531999999</v>
       </c>
       <c r="O83">
-        <v>-118.2333740676</v>
+        <v>-119.9666601672</v>
       </c>
       <c r="P83">
-        <v>-691.5842565324</v>
+        <v>-701.7227930327999</v>
       </c>
       <c r="Q83">
-        <v>-574.8842565323999</v>
+        <v>-585.0227930327999</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2300869796052489</v>
+        <v>0.2403251451388739</v>
       </c>
       <c r="T83">
-        <v>4.25605033730367</v>
+        <v>4.492497578264985</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.0230474143721466</v>
+        <v>0.02276634834321798</v>
       </c>
       <c r="W83">
-        <v>0.2303654196910478</v>
+        <v>0.2304316950606692</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.1578590025489492</v>
+        <v>0.1559338927617671</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2322125160747461</v>
+        <v>0.234112516074746</v>
       </c>
       <c r="C84">
-        <v>-3092.585823875883</v>
+        <v>-3152.500485558915</v>
       </c>
       <c r="D84">
-        <v>958.4681761241168</v>
+        <v>948.9005144410855</v>
       </c>
       <c r="E84">
-        <v>3182.354</v>
+        <v>3232.701</v>
       </c>
       <c r="F84">
-        <v>4128.454</v>
+        <v>4178.801</v>
       </c>
       <c r="G84">
         <v>77.40000000000001</v>
@@ -8181,37 +8181,37 @@
         <v>151.8</v>
       </c>
       <c r="M84">
-        <v>973.4894532</v>
+        <v>985.3612758000002</v>
       </c>
       <c r="N84">
-        <v>-821.6894531999999</v>
+        <v>-833.5612758000002</v>
       </c>
       <c r="O84">
-        <v>-119.9666601672</v>
+        <v>-121.6999462668</v>
       </c>
       <c r="P84">
-        <v>-701.7227930327999</v>
+        <v>-711.8613295332002</v>
       </c>
       <c r="Q84">
-        <v>-585.0227930327999</v>
+        <v>-595.1613295332002</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2403251451388739</v>
+        <v>0.2517678007352782</v>
       </c>
       <c r="T84">
-        <v>4.492497578264985</v>
+        <v>4.756762141692338</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.02276634834321798</v>
+        <v>0.02249205498968523</v>
       </c>
       <c r="W84">
-        <v>0.2304316950606692</v>
+        <v>0.2304963734334322</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.1559338927617671</v>
+        <v>0.1540551711622276</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.234112516074746</v>
+        <v>0.236012516074746</v>
       </c>
       <c r="C85">
-        <v>-3152.500485558915</v>
+        <v>-3212.226021702362</v>
       </c>
       <c r="D85">
-        <v>948.9005144410855</v>
+        <v>939.5219782976378</v>
       </c>
       <c r="E85">
-        <v>3232.701</v>
+        <v>3283.048</v>
       </c>
       <c r="F85">
-        <v>4178.801</v>
+        <v>4229.148</v>
       </c>
       <c r="G85">
         <v>77.40000000000001</v>
@@ -8263,37 +8263,37 @@
         <v>151.8</v>
       </c>
       <c r="M85">
-        <v>985.3612758000002</v>
+        <v>997.2330984</v>
       </c>
       <c r="N85">
-        <v>-833.5612758000002</v>
+        <v>-845.4330984000001</v>
       </c>
       <c r="O85">
-        <v>-121.6999462668</v>
+        <v>-123.4332323664</v>
       </c>
       <c r="P85">
-        <v>-711.8613295332002</v>
+        <v>-721.9998660336</v>
       </c>
       <c r="Q85">
-        <v>-595.1613295332002</v>
+        <v>-605.2998660336</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2517678007352782</v>
+        <v>0.2646407882812332</v>
       </c>
       <c r="T85">
-        <v>4.756762141692338</v>
+        <v>5.054059775548111</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.02249205498968523</v>
+        <v>0.02222429243028422</v>
       </c>
       <c r="W85">
-        <v>0.2304963734334322</v>
+        <v>0.230559511844939</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.1540551711622276</v>
+        <v>0.1522211810293439</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.236012516074746</v>
+        <v>0.2379125160747461</v>
       </c>
       <c r="C86">
-        <v>-3212.226021702362</v>
+        <v>-3271.767985137755</v>
       </c>
       <c r="D86">
-        <v>939.5219782976378</v>
+        <v>930.3270148622445</v>
       </c>
       <c r="E86">
-        <v>3283.048</v>
+        <v>3333.395</v>
       </c>
       <c r="F86">
-        <v>4229.148</v>
+        <v>4279.495</v>
       </c>
       <c r="G86">
         <v>77.40000000000001</v>
@@ -8345,37 +8345,37 @@
         <v>151.8</v>
       </c>
       <c r="M86">
-        <v>997.2330984</v>
+        <v>1009.104921</v>
       </c>
       <c r="N86">
-        <v>-845.4330984000001</v>
+        <v>-857.3049209999999</v>
       </c>
       <c r="O86">
-        <v>-123.4332323664</v>
+        <v>-125.166518466</v>
       </c>
       <c r="P86">
-        <v>-721.9998660336</v>
+        <v>-732.138402534</v>
       </c>
       <c r="Q86">
-        <v>-605.2998660336</v>
+        <v>-615.4384025339999</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.264640788281233</v>
+        <v>0.2792301741666485</v>
       </c>
       <c r="T86">
-        <v>5.054059775548106</v>
+        <v>5.390997093917981</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.02222429243028422</v>
+        <v>0.02196283016639853</v>
       </c>
       <c r="W86">
-        <v>0.230559511844939</v>
+        <v>0.2306211646467632</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.1522211810293439</v>
+        <v>0.1504303436054694</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2379125160747461</v>
+        <v>0.239812516074746</v>
       </c>
       <c r="C87">
-        <v>-3271.767985137755</v>
+        <v>-3331.131713424477</v>
       </c>
       <c r="D87">
-        <v>930.3270148622445</v>
+        <v>921.3102865755226</v>
       </c>
       <c r="E87">
-        <v>3333.395</v>
+        <v>3383.742</v>
       </c>
       <c r="F87">
-        <v>4279.495</v>
+        <v>4329.842</v>
       </c>
       <c r="G87">
         <v>77.40000000000001</v>
@@ -8427,37 +8427,37 @@
         <v>151.8</v>
       </c>
       <c r="M87">
-        <v>1009.104921</v>
+        <v>1020.9767436</v>
       </c>
       <c r="N87">
-        <v>-857.3049209999999</v>
+        <v>-869.1767436</v>
       </c>
       <c r="O87">
-        <v>-125.166518466</v>
+        <v>-126.8998045656</v>
       </c>
       <c r="P87">
-        <v>-732.138402534</v>
+        <v>-742.2769390344</v>
       </c>
       <c r="Q87">
-        <v>-615.4384025339999</v>
+        <v>-625.5769390344</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2792301741666485</v>
+        <v>0.2959037580356949</v>
       </c>
       <c r="T87">
-        <v>5.390997093917981</v>
+        <v>5.776068314912123</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.02196283016639853</v>
+        <v>0.02170744842027761</v>
       </c>
       <c r="W87">
-        <v>0.2306211646467632</v>
+        <v>0.2306813836624985</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.1504303436054694</v>
+        <v>0.1486811535635453</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.239812516074746</v>
+        <v>0.241712516074746</v>
       </c>
       <c r="C88">
-        <v>-3331.131713424477</v>
+        <v>-3390.322339181716</v>
       </c>
       <c r="D88">
-        <v>921.3102865755226</v>
+        <v>912.4666608182837</v>
       </c>
       <c r="E88">
-        <v>3383.742</v>
+        <v>3434.088999999999</v>
       </c>
       <c r="F88">
-        <v>4329.842</v>
+        <v>4380.188999999999</v>
       </c>
       <c r="G88">
         <v>77.40000000000001</v>
@@ -8509,37 +8509,37 @@
         <v>151.8</v>
       </c>
       <c r="M88">
-        <v>1020.9767436</v>
+        <v>1032.8485662</v>
       </c>
       <c r="N88">
-        <v>-869.1767436</v>
+        <v>-881.0485661999999</v>
       </c>
       <c r="O88">
-        <v>-126.8998045656</v>
+        <v>-128.6330906652</v>
       </c>
       <c r="P88">
-        <v>-742.2769390344</v>
+        <v>-752.4154755348</v>
       </c>
       <c r="Q88">
-        <v>-625.5769390344</v>
+        <v>-635.7154755347999</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2959037580356949</v>
+        <v>0.3151425086538253</v>
       </c>
       <c r="T88">
-        <v>5.776068314912123</v>
+        <v>6.220381262213055</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.02170744842027761</v>
+        <v>0.02145793751889511</v>
       </c>
       <c r="W88">
-        <v>0.2306813836624985</v>
+        <v>0.2307402183330445</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.1486811535635453</v>
+        <v>0.1469721747869528</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.241712516074746</v>
+        <v>0.243612516074746</v>
       </c>
       <c r="C89">
-        <v>-3390.322339181716</v>
+        <v>-3449.344799831015</v>
       </c>
       <c r="D89">
-        <v>912.4666608182837</v>
+        <v>903.7912001689847</v>
       </c>
       <c r="E89">
-        <v>3434.088999999999</v>
+        <v>3484.436</v>
       </c>
       <c r="F89">
-        <v>4380.188999999999</v>
+        <v>4430.536</v>
       </c>
       <c r="G89">
         <v>77.40000000000001</v>
@@ -8591,37 +8591,37 @@
         <v>151.8</v>
       </c>
       <c r="M89">
-        <v>1032.8485662</v>
+        <v>1044.7203888</v>
       </c>
       <c r="N89">
-        <v>-881.0485661999999</v>
+        <v>-892.9203888000002</v>
       </c>
       <c r="O89">
-        <v>-128.6330906652</v>
+        <v>-130.3663767648</v>
       </c>
       <c r="P89">
-        <v>-752.4154755348</v>
+        <v>-762.5540120352002</v>
       </c>
       <c r="Q89">
-        <v>-635.7154755347999</v>
+        <v>-645.8540120352002</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3151425086538253</v>
+        <v>0.3375877177083108</v>
       </c>
       <c r="T89">
-        <v>6.220381262213055</v>
+        <v>6.738746367397477</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.02145793751889511</v>
+        <v>0.02121409731981675</v>
       </c>
       <c r="W89">
-        <v>0.2307402183330445</v>
+        <v>0.2307977158519872</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.1469721747869528</v>
+        <v>0.145302036437101</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.243612516074746</v>
+        <v>0.245512516074746</v>
       </c>
       <c r="C90">
-        <v>-3449.344799831015</v>
+        <v>-3508.203846788282</v>
       </c>
       <c r="D90">
-        <v>903.7912001689847</v>
+        <v>895.2791532117175</v>
       </c>
       <c r="E90">
-        <v>3484.436</v>
+        <v>3534.783</v>
       </c>
       <c r="F90">
-        <v>4430.536</v>
+        <v>4480.883</v>
       </c>
       <c r="G90">
         <v>77.40000000000001</v>
@@ -8673,37 +8673,37 @@
         <v>151.8</v>
       </c>
       <c r="M90">
-        <v>1044.7203888</v>
+        <v>1056.5922114</v>
       </c>
       <c r="N90">
-        <v>-892.9203888000002</v>
+        <v>-904.7922114</v>
       </c>
       <c r="O90">
-        <v>-130.3663767648</v>
+        <v>-132.0996628644</v>
       </c>
       <c r="P90">
-        <v>-762.5540120352002</v>
+        <v>-772.6925485356001</v>
       </c>
       <c r="Q90">
-        <v>-645.8540120352002</v>
+        <v>-655.9925485356</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3375877177083108</v>
+        <v>0.3641138738636117</v>
       </c>
       <c r="T90">
-        <v>6.738746367397477</v>
+        <v>7.351359673524519</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.02121409731981675</v>
+        <v>0.02097573667577387</v>
       </c>
       <c r="W90">
-        <v>0.2307977158519872</v>
+        <v>0.2308539212918525</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.145302036437101</v>
+        <v>0.1436694292861224</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.245512516074746</v>
+        <v>0.247412516074746</v>
       </c>
       <c r="C91">
-        <v>-3508.203846788282</v>
+        <v>-3566.904054141216</v>
       </c>
       <c r="D91">
-        <v>895.2791532117175</v>
+        <v>886.9259458587833</v>
       </c>
       <c r="E91">
-        <v>3534.783</v>
+        <v>3585.13</v>
       </c>
       <c r="F91">
-        <v>4480.883</v>
+        <v>4531.23</v>
       </c>
       <c r="G91">
         <v>77.40000000000001</v>
@@ -8755,37 +8755,37 @@
         <v>151.8</v>
       </c>
       <c r="M91">
-        <v>1056.5922114</v>
+        <v>1068.464034</v>
       </c>
       <c r="N91">
-        <v>-904.7922114</v>
+        <v>-916.6640339999999</v>
       </c>
       <c r="O91">
-        <v>-132.0996628644</v>
+        <v>-133.832948964</v>
       </c>
       <c r="P91">
-        <v>-772.6925485356001</v>
+        <v>-782.8310850359999</v>
       </c>
       <c r="Q91">
-        <v>-655.9925485356</v>
+        <v>-666.1310850359998</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3641138738636117</v>
+        <v>0.3959452612499729</v>
       </c>
       <c r="T91">
-        <v>7.351359673524519</v>
+        <v>8.086495640876972</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.02097573667577387</v>
+        <v>0.02074267293493194</v>
       </c>
       <c r="W91">
-        <v>0.2308539212918525</v>
+        <v>0.2309088777219431</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.1436694292861224</v>
+        <v>0.1420731022940543</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.247412516074746</v>
+        <v>0.249312516074746</v>
       </c>
       <c r="C92">
-        <v>-3566.904054141216</v>
+        <v>-3625.449826845446</v>
       </c>
       <c r="D92">
-        <v>886.9259458587833</v>
+        <v>878.7271731545543</v>
       </c>
       <c r="E92">
-        <v>3585.13</v>
+        <v>3635.477</v>
       </c>
       <c r="F92">
-        <v>4531.23</v>
+        <v>4581.577</v>
       </c>
       <c r="G92">
         <v>77.40000000000001</v>
@@ -8837,37 +8837,37 @@
         <v>151.8</v>
       </c>
       <c r="M92">
-        <v>1068.464034</v>
+        <v>1080.3358566</v>
       </c>
       <c r="N92">
-        <v>-916.6640339999999</v>
+        <v>-928.5358566000002</v>
       </c>
       <c r="O92">
-        <v>-133.832948964</v>
+        <v>-135.5662350636</v>
       </c>
       <c r="P92">
-        <v>-782.8310850359999</v>
+        <v>-792.9696215364002</v>
       </c>
       <c r="Q92">
-        <v>-666.1310850359998</v>
+        <v>-676.2696215364001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3959452612499729</v>
+        <v>0.4348502902777477</v>
       </c>
       <c r="T92">
-        <v>8.086495640876972</v>
+        <v>8.984995156529971</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.02074267293493194</v>
+        <v>0.02051473147410851</v>
       </c>
       <c r="W92">
-        <v>0.2309088777219431</v>
+        <v>0.2309626263184052</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.1420731022940543</v>
+        <v>0.1405118594117021</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.249312516074746</v>
+        <v>0.251212516074746</v>
       </c>
       <c r="C93">
-        <v>-3625.449826845446</v>
+        <v>-3683.845408470238</v>
       </c>
       <c r="D93">
-        <v>878.7271731545543</v>
+        <v>870.678591529762</v>
       </c>
       <c r="E93">
-        <v>3635.477</v>
+        <v>3685.824</v>
       </c>
       <c r="F93">
-        <v>4581.577</v>
+        <v>4631.924</v>
       </c>
       <c r="G93">
         <v>77.40000000000001</v>
@@ -8919,37 +8919,37 @@
         <v>151.8</v>
       </c>
       <c r="M93">
-        <v>1080.3358566</v>
+        <v>1092.2076792</v>
       </c>
       <c r="N93">
-        <v>-928.5358566000002</v>
+        <v>-940.4076792000001</v>
       </c>
       <c r="O93">
-        <v>-135.5662350636</v>
+        <v>-137.2995211632</v>
       </c>
       <c r="P93">
-        <v>-792.9696215364002</v>
+        <v>-803.1081580368001</v>
       </c>
       <c r="Q93">
-        <v>-676.2696215364001</v>
+        <v>-686.4081580368</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4348502902777477</v>
+        <v>0.4834815765624664</v>
       </c>
       <c r="T93">
-        <v>8.984995156529971</v>
+        <v>10.10811955109622</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.02051473147410851</v>
+        <v>0.02029174526243342</v>
       </c>
       <c r="W93">
-        <v>0.2309626263184052</v>
+        <v>0.2310152064671182</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1405118594117021</v>
+        <v>0.1389845565920097</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.251212516074746</v>
+        <v>0.2531125160747461</v>
       </c>
       <c r="C94">
-        <v>-3683.845408470238</v>
+        <v>-3742.094888522402</v>
       </c>
       <c r="D94">
-        <v>870.678591529762</v>
+        <v>862.7761114775975</v>
       </c>
       <c r="E94">
-        <v>3685.824</v>
+        <v>3736.171</v>
       </c>
       <c r="F94">
-        <v>4631.924</v>
+        <v>4682.271</v>
       </c>
       <c r="G94">
         <v>77.40000000000001</v>
@@ -9001,37 +9001,37 @@
         <v>151.8</v>
       </c>
       <c r="M94">
-        <v>1092.2076792</v>
+        <v>1104.0795018</v>
       </c>
       <c r="N94">
-        <v>-940.4076792000001</v>
+        <v>-952.2795017999999</v>
       </c>
       <c r="O94">
-        <v>-137.2995211632</v>
+        <v>-139.0328072628</v>
       </c>
       <c r="P94">
-        <v>-803.1081580368001</v>
+        <v>-813.2466945371999</v>
       </c>
       <c r="Q94">
-        <v>-686.4081580368</v>
+        <v>-696.5466945371999</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4834815765624664</v>
+        <v>0.5460075160713901</v>
       </c>
       <c r="T94">
-        <v>10.10811955109622</v>
+        <v>11.55213662982425</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.02029174526243342</v>
+        <v>0.02007355445315994</v>
       </c>
       <c r="W94">
-        <v>0.2310152064671182</v>
+        <v>0.2310666558599449</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1389845565920097</v>
+        <v>0.1374900989942461</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2531125160747461</v>
+        <v>0.2550125160747461</v>
       </c>
       <c r="C95">
-        <v>-3742.094888522402</v>
+        <v>-3800.202209374933</v>
       </c>
       <c r="D95">
-        <v>862.7761114775975</v>
+        <v>855.0157906250672</v>
       </c>
       <c r="E95">
-        <v>3736.171</v>
+        <v>3786.518</v>
       </c>
       <c r="F95">
-        <v>4682.271</v>
+        <v>4732.618</v>
       </c>
       <c r="G95">
         <v>77.40000000000001</v>
@@ -9083,37 +9083,37 @@
         <v>151.8</v>
       </c>
       <c r="M95">
-        <v>1104.0795018</v>
+        <v>1115.9513244</v>
       </c>
       <c r="N95">
-        <v>-952.2795017999999</v>
+        <v>-964.1513244000002</v>
       </c>
       <c r="O95">
-        <v>-139.0328072628</v>
+        <v>-140.7660933624</v>
       </c>
       <c r="P95">
-        <v>-813.2466945371999</v>
+        <v>-823.3852310376002</v>
       </c>
       <c r="Q95">
-        <v>-696.5466945371999</v>
+        <v>-706.6852310376001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5460075160713901</v>
+        <v>0.6293754354166219</v>
       </c>
       <c r="T95">
-        <v>11.55213662982425</v>
+        <v>13.47749273479496</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.02007355445315994</v>
+        <v>0.01986000600153058</v>
       </c>
       <c r="W95">
-        <v>0.2310666558599449</v>
+        <v>0.2311170105848391</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1374900989942461</v>
+        <v>0.1360274383666478</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2550125160747461</v>
+        <v>0.2569125160747461</v>
       </c>
       <c r="C96">
-        <v>-3800.202209374933</v>
+        <v>-3858.171172825067</v>
       </c>
       <c r="D96">
-        <v>855.0157906250672</v>
+        <v>847.3938271749331</v>
       </c>
       <c r="E96">
-        <v>3786.518</v>
+        <v>3836.865</v>
       </c>
       <c r="F96">
-        <v>4732.618</v>
+        <v>4782.965</v>
       </c>
       <c r="G96">
         <v>77.40000000000001</v>
@@ -9165,37 +9165,37 @@
         <v>151.8</v>
       </c>
       <c r="M96">
-        <v>1115.9513244</v>
+        <v>1127.823147</v>
       </c>
       <c r="N96">
-        <v>-964.1513244000002</v>
+        <v>-976.0231470000001</v>
       </c>
       <c r="O96">
-        <v>-140.7660933624</v>
+        <v>-142.499379462</v>
       </c>
       <c r="P96">
-        <v>-823.3852310376002</v>
+        <v>-833.5237675380001</v>
       </c>
       <c r="Q96">
-        <v>-706.6852310376001</v>
+        <v>-716.8237675380001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6293754354166219</v>
+        <v>0.7460905224999467</v>
       </c>
       <c r="T96">
-        <v>13.47749273479496</v>
+        <v>16.17299128175397</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.01986000600153058</v>
+        <v>0.01965095330677763</v>
       </c>
       <c r="W96">
-        <v>0.2311170105848391</v>
+        <v>0.2311663052102619</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1360274383666478</v>
+        <v>0.1345955705943672</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2569125160747461</v>
+        <v>0.258812516074746</v>
       </c>
       <c r="C97">
-        <v>-3858.171172825067</v>
+        <v>-3916.005446304676</v>
       </c>
       <c r="D97">
-        <v>847.3938271749331</v>
+        <v>839.9065536953242</v>
       </c>
       <c r="E97">
-        <v>3836.865</v>
+        <v>3887.212</v>
       </c>
       <c r="F97">
-        <v>4782.965</v>
+        <v>4833.312</v>
       </c>
       <c r="G97">
         <v>77.40000000000001</v>
@@ -9247,37 +9247,37 @@
         <v>151.8</v>
       </c>
       <c r="M97">
-        <v>1127.823147</v>
+        <v>1139.6949696</v>
       </c>
       <c r="N97">
-        <v>-976.0231470000001</v>
+        <v>-987.8949696</v>
       </c>
       <c r="O97">
-        <v>-142.499379462</v>
+        <v>-144.2326655616</v>
       </c>
       <c r="P97">
-        <v>-833.5237675380001</v>
+        <v>-843.6623040384</v>
       </c>
       <c r="Q97">
-        <v>-716.8237675380001</v>
+        <v>-726.9623040383999</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7460905224999467</v>
+        <v>0.9211631531249336</v>
       </c>
       <c r="T97">
-        <v>16.17299128175397</v>
+        <v>20.21623910219246</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.01965095330677763</v>
+        <v>0.0194462558764987</v>
       </c>
       <c r="W97">
-        <v>0.2311663052102619</v>
+        <v>0.2312145728643216</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1345955705943672</v>
+        <v>0.133193533400676</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.258812516074746</v>
+        <v>0.260712516074746</v>
       </c>
       <c r="C98">
-        <v>-3916.005446304676</v>
+        <v>-3973.708568764299</v>
       </c>
       <c r="D98">
-        <v>839.9065536953242</v>
+        <v>832.5504312357004</v>
       </c>
       <c r="E98">
-        <v>3887.212</v>
+        <v>3937.559</v>
       </c>
       <c r="F98">
-        <v>4833.312</v>
+        <v>4883.659</v>
       </c>
       <c r="G98">
         <v>77.40000000000001</v>
@@ -9329,37 +9329,37 @@
         <v>151.8</v>
       </c>
       <c r="M98">
-        <v>1139.6949696</v>
+        <v>1151.5667922</v>
       </c>
       <c r="N98">
-        <v>-987.8949696</v>
+        <v>-999.7667922000001</v>
       </c>
       <c r="O98">
-        <v>-144.2326655616</v>
+        <v>-145.9659516612</v>
       </c>
       <c r="P98">
-        <v>-843.6623040384</v>
+        <v>-853.8008405388</v>
       </c>
       <c r="Q98">
-        <v>-726.9623040383999</v>
+        <v>-737.1008405388</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.9211631531249314</v>
+        <v>1.212950870833242</v>
       </c>
       <c r="T98">
-        <v>20.21623910219241</v>
+        <v>26.95498546958988</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.0194462558764987</v>
+        <v>0.01924577901179252</v>
       </c>
       <c r="W98">
-        <v>0.2312145728643216</v>
+        <v>0.2312618453090193</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.133193533400676</v>
+        <v>0.1318204041903597</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.260712516074746</v>
+        <v>0.2626125160747461</v>
       </c>
       <c r="C99">
-        <v>-3973.708568764299</v>
+        <v>-4031.283956250664</v>
       </c>
       <c r="D99">
-        <v>832.5504312357004</v>
+        <v>825.3220437493356</v>
       </c>
       <c r="E99">
-        <v>3937.559</v>
+        <v>3987.905999999999</v>
       </c>
       <c r="F99">
-        <v>4883.659</v>
+        <v>4934.005999999999</v>
       </c>
       <c r="G99">
         <v>77.40000000000001</v>
@@ -9411,37 +9411,37 @@
         <v>151.8</v>
       </c>
       <c r="M99">
-        <v>1151.5667922</v>
+        <v>1163.4386148</v>
       </c>
       <c r="N99">
-        <v>-999.7667922000001</v>
+        <v>-1011.6386148</v>
       </c>
       <c r="O99">
-        <v>-145.9659516612</v>
+        <v>-147.6992377608</v>
       </c>
       <c r="P99">
-        <v>-853.8008405388</v>
+        <v>-863.9393770391999</v>
       </c>
       <c r="Q99">
-        <v>-737.1008405388</v>
+        <v>-747.2393770391999</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.212950870833242</v>
+        <v>1.796526306249863</v>
       </c>
       <c r="T99">
-        <v>26.95498546958988</v>
+        <v>40.43247820438482</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.01924577901179252</v>
+        <v>0.01904939351167219</v>
       </c>
       <c r="W99">
-        <v>0.2312618453090193</v>
+        <v>0.2313081530099477</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1318204041903597</v>
+        <v>0.130475298025152</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2626125160747461</v>
+        <v>0.264512516074746</v>
       </c>
       <c r="C100">
-        <v>-4031.283956250664</v>
+        <v>-4088.734907196148</v>
       </c>
       <c r="D100">
-        <v>825.3220437493356</v>
+        <v>818.2180928038515</v>
       </c>
       <c r="E100">
-        <v>3987.905999999999</v>
+        <v>4038.253</v>
       </c>
       <c r="F100">
-        <v>4934.005999999999</v>
+        <v>4984.353</v>
       </c>
       <c r="G100">
         <v>77.40000000000001</v>
@@ -9493,37 +9493,37 @@
         <v>151.8</v>
       </c>
       <c r="M100">
-        <v>1163.4386148</v>
+        <v>1175.3104374</v>
       </c>
       <c r="N100">
-        <v>-1011.6386148</v>
+        <v>-1023.5104374</v>
       </c>
       <c r="O100">
-        <v>-147.6992377608</v>
+        <v>-149.4325238604</v>
       </c>
       <c r="P100">
-        <v>-863.9393770391999</v>
+        <v>-874.0779135396</v>
       </c>
       <c r="Q100">
-        <v>-747.2393770391999</v>
+        <v>-757.3779135395999</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.796526306249863</v>
+        <v>3.547252612499725</v>
       </c>
       <c r="T100">
-        <v>40.43247820438482</v>
+        <v>80.86495640876964</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.01904939351167219</v>
+        <v>0.01885697539539267</v>
       </c>
       <c r="W100">
-        <v>0.2313081530099477</v>
+        <v>0.2313535252017664</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.130475298025152</v>
+        <v>0.1291573657218675</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.264512516074746</v>
-      </c>
-      <c r="C101">
-        <v>-4088.734907196148</v>
-      </c>
-      <c r="D101">
-        <v>818.2180928038515</v>
-      </c>
-      <c r="E101">
-        <v>4038.253</v>
-      </c>
-      <c r="F101">
-        <v>4984.353</v>
-      </c>
-      <c r="G101">
-        <v>77.40000000000001</v>
-      </c>
-      <c r="H101">
-        <v>4088.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>268.5</v>
-      </c>
-      <c r="K101">
-        <v>116.7</v>
-      </c>
-      <c r="L101">
-        <v>151.8</v>
-      </c>
-      <c r="M101">
-        <v>1175.3104374</v>
-      </c>
-      <c r="N101">
-        <v>-1023.5104374</v>
-      </c>
-      <c r="O101">
-        <v>-149.4325238604</v>
-      </c>
-      <c r="P101">
-        <v>-874.0779135396</v>
-      </c>
-      <c r="Q101">
-        <v>-757.3779135395999</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.547252612499725</v>
-      </c>
-      <c r="T101">
-        <v>80.86495640876964</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.01885697539539267</v>
-      </c>
-      <c r="W101">
-        <v>0.2313535252017664</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1291573657218675</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
